--- a/data_lake/industry/Automobile/MUVVI.xlsx
+++ b/data_lake/industry/Automobile/MUVVI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/industry/Automobile/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data_lake\industry\Automobile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBD69D2F-B05B-3543-A45B-3827A8114E3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08DCE10B-8D19-4001-81A4-EAE33BC556EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22160" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11430" yWindow="0" windowWidth="11700" windowHeight="14730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MANHEIM" sheetId="1" r:id="rId1"/>
@@ -168,7 +168,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="5" applyFont="1"/>
     <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
@@ -206,10 +206,11 @@
     <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="7" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="5" applyFont="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="Comma" xfId="5" builtinId="3"/>
@@ -522,24 +523,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O361"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.1640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1796875" style="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.33203125" style="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="7.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="8.83203125" style="7"/>
-    <col min="14" max="14" width="20.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.83203125" style="7"/>
+    <col min="4" max="4" width="10.81640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="8.81640625" style="7"/>
+    <col min="14" max="14" width="20.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.81640625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
@@ -552,19 +553,19 @@
       <c r="D1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="G1" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="I1" s="23" t="s">
         <v>12</v>
       </c>
       <c r="J1" s="22" t="s">
@@ -574,7 +575,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="9">
         <v>35431</v>
       </c>
@@ -612,14 +613,10 @@
       <c r="G2" s="2">
         <v>9011</v>
       </c>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
       <c r="L2" s="12"/>
-      <c r="N2" s="21"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N2" s="20"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="9">
         <v>35462</v>
       </c>
@@ -657,14 +654,10 @@
       <c r="G3" s="2">
         <v>9138</v>
       </c>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
       <c r="L3" s="12"/>
-      <c r="N3" s="21"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N3" s="20"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="9">
         <v>35490</v>
       </c>
@@ -687,14 +680,10 @@
       <c r="G4" s="2">
         <v>9284</v>
       </c>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
       <c r="L4" s="12"/>
-      <c r="N4" s="21"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N4" s="20"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="9">
         <v>35521</v>
       </c>
@@ -717,14 +706,10 @@
       <c r="G5" s="2">
         <v>9271</v>
       </c>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
       <c r="L5" s="12"/>
-      <c r="N5" s="21"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N5" s="20"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="9">
         <v>35551</v>
       </c>
@@ -747,14 +732,10 @@
       <c r="G6" s="2">
         <v>9291</v>
       </c>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
       <c r="L6" s="12"/>
-      <c r="N6" s="21"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N6" s="20"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="9">
         <v>35582</v>
       </c>
@@ -777,14 +758,10 @@
       <c r="G7" s="2">
         <v>9210</v>
       </c>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
       <c r="L7" s="12"/>
-      <c r="N7" s="21"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N7" s="20"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="9">
         <v>35612</v>
       </c>
@@ -807,14 +784,10 @@
       <c r="G8" s="2">
         <v>9255</v>
       </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
       <c r="L8" s="12"/>
-      <c r="N8" s="21"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N8" s="20"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="9">
         <v>35643</v>
       </c>
@@ -837,14 +810,10 @@
       <c r="G9" s="2">
         <v>9382</v>
       </c>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
       <c r="L9" s="12"/>
-      <c r="N9" s="21"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N9" s="20"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="9">
         <v>35674</v>
       </c>
@@ -867,14 +836,10 @@
       <c r="G10" s="2">
         <v>9257</v>
       </c>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
       <c r="L10" s="12"/>
-      <c r="N10" s="21"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N10" s="20"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="9">
         <v>35704</v>
       </c>
@@ -897,14 +862,10 @@
       <c r="G11" s="2">
         <v>9085</v>
       </c>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
       <c r="L11" s="12"/>
-      <c r="N11" s="21"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N11" s="20"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="9">
         <v>35735</v>
       </c>
@@ -927,14 +888,10 @@
       <c r="G12" s="2">
         <v>8902</v>
       </c>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
       <c r="L12" s="12"/>
-      <c r="N12" s="21"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N12" s="20"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="9">
         <v>35765</v>
       </c>
@@ -957,14 +914,10 @@
       <c r="G13" s="2">
         <v>8900</v>
       </c>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
       <c r="L13" s="12"/>
-      <c r="N13" s="21"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="20"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="9">
         <v>35796</v>
       </c>
@@ -987,14 +940,10 @@
       <c r="G14" s="2">
         <v>9059</v>
       </c>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
       <c r="L14" s="12"/>
-      <c r="N14" s="21"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N14" s="20"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="9">
         <v>35827</v>
       </c>
@@ -1017,14 +966,10 @@
       <c r="G15" s="2">
         <v>9185</v>
       </c>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="12"/>
       <c r="L15" s="12"/>
-      <c r="N15" s="21"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N15" s="20"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="9">
         <v>35855</v>
       </c>
@@ -1047,14 +992,10 @@
       <c r="G16" s="2">
         <v>9407</v>
       </c>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
       <c r="L16" s="12"/>
-      <c r="N16" s="21"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N16" s="20"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="9">
         <v>35886</v>
       </c>
@@ -1077,14 +1018,10 @@
       <c r="G17" s="2">
         <v>9563</v>
       </c>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
       <c r="L17" s="12"/>
-      <c r="N17" s="21"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N17" s="20"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="9">
         <v>35916</v>
       </c>
@@ -1107,14 +1044,10 @@
       <c r="G18" s="2">
         <v>9486</v>
       </c>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
       <c r="L18" s="12"/>
-      <c r="N18" s="21"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N18" s="20"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="9">
         <v>35947</v>
       </c>
@@ -1137,14 +1070,10 @@
       <c r="G19" s="2">
         <v>9516</v>
       </c>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="12"/>
       <c r="L19" s="12"/>
-      <c r="N19" s="21"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N19" s="20"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="9">
         <v>35977</v>
       </c>
@@ -1167,14 +1096,10 @@
       <c r="G20" s="2">
         <v>9770</v>
       </c>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="12"/>
       <c r="L20" s="12"/>
-      <c r="N20" s="21"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N20" s="20"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="9">
         <v>36008</v>
       </c>
@@ -1197,14 +1122,10 @@
       <c r="G21" s="2">
         <v>9752</v>
       </c>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="12"/>
       <c r="L21" s="12"/>
-      <c r="N21" s="21"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N21" s="20"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="9">
         <v>36039</v>
       </c>
@@ -1227,14 +1148,10 @@
       <c r="G22" s="2">
         <v>9835</v>
       </c>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="12"/>
       <c r="L22" s="12"/>
-      <c r="N22" s="21"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N22" s="20"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="9">
         <v>36069</v>
       </c>
@@ -1257,14 +1174,10 @@
       <c r="G23" s="2">
         <v>9651</v>
       </c>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="12"/>
       <c r="L23" s="12"/>
-      <c r="N23" s="21"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N23" s="20"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="9">
         <v>36100</v>
       </c>
@@ -1287,14 +1200,10 @@
       <c r="G24" s="2">
         <v>9625</v>
       </c>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
-      <c r="K24" s="12"/>
       <c r="L24" s="12"/>
-      <c r="N24" s="21"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N24" s="20"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="9">
         <v>36130</v>
       </c>
@@ -1317,14 +1226,10 @@
       <c r="G25" s="2">
         <v>9641</v>
       </c>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
       <c r="L25" s="12"/>
-      <c r="N25" s="21"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="20"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="9">
         <v>36161</v>
       </c>
@@ -1347,14 +1252,10 @@
       <c r="G26" s="2">
         <v>9804</v>
       </c>
-      <c r="H26" s="12"/>
-      <c r="I26" s="12"/>
-      <c r="J26" s="12"/>
-      <c r="K26" s="12"/>
       <c r="L26" s="12"/>
-      <c r="N26" s="21"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N26" s="20"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="9">
         <v>36192</v>
       </c>
@@ -1377,14 +1278,10 @@
       <c r="G27" s="2">
         <v>9927</v>
       </c>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
       <c r="L27" s="12"/>
-      <c r="N27" s="21"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N27" s="20"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="9">
         <v>36220</v>
       </c>
@@ -1407,14 +1304,10 @@
       <c r="G28" s="2">
         <v>10039</v>
       </c>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
       <c r="L28" s="12"/>
-      <c r="N28" s="21"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="20"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="9">
         <v>36251</v>
       </c>
@@ -1437,14 +1330,10 @@
       <c r="G29" s="2">
         <v>10080</v>
       </c>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
       <c r="L29" s="12"/>
-      <c r="N29" s="21"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N29" s="20"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="9">
         <v>36281</v>
       </c>
@@ -1467,14 +1356,10 @@
       <c r="G30" s="2">
         <v>10096</v>
       </c>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
       <c r="L30" s="12"/>
-      <c r="N30" s="21"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="20"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="9">
         <v>36312</v>
       </c>
@@ -1497,14 +1382,10 @@
       <c r="G31" s="2">
         <v>10146</v>
       </c>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
       <c r="L31" s="12"/>
-      <c r="N31" s="21"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="20"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="9">
         <v>36342</v>
       </c>
@@ -1527,14 +1408,10 @@
       <c r="G32" s="2">
         <v>10161</v>
       </c>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
       <c r="L32" s="12"/>
-      <c r="N32" s="21"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N32" s="20"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="9">
         <v>36373</v>
       </c>
@@ -1557,14 +1434,10 @@
       <c r="G33" s="2">
         <v>10191</v>
       </c>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
       <c r="L33" s="12"/>
-      <c r="N33" s="21"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N33" s="20"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="9">
         <v>36404</v>
       </c>
@@ -1587,14 +1460,10 @@
       <c r="G34" s="2">
         <v>10125</v>
       </c>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="12"/>
-      <c r="K34" s="12"/>
       <c r="L34" s="12"/>
-      <c r="N34" s="21"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="20"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="9">
         <v>36434</v>
       </c>
@@ -1617,14 +1486,10 @@
       <c r="G35" s="2">
         <v>9851</v>
       </c>
-      <c r="H35" s="12"/>
-      <c r="I35" s="12"/>
-      <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
       <c r="L35" s="12"/>
-      <c r="N35" s="21"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N35" s="20"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="9">
         <v>36465</v>
       </c>
@@ -1647,14 +1512,10 @@
       <c r="G36" s="2">
         <v>9745</v>
       </c>
-      <c r="H36" s="12"/>
-      <c r="I36" s="12"/>
-      <c r="J36" s="12"/>
-      <c r="K36" s="12"/>
       <c r="L36" s="12"/>
-      <c r="N36" s="21"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N36" s="20"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="9">
         <v>36495</v>
       </c>
@@ -1677,14 +1538,10 @@
       <c r="G37" s="2">
         <v>9769</v>
       </c>
-      <c r="H37" s="12"/>
-      <c r="I37" s="12"/>
-      <c r="J37" s="12"/>
-      <c r="K37" s="12"/>
       <c r="L37" s="12"/>
-      <c r="N37" s="21"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N37" s="20"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="9">
         <v>36526</v>
       </c>
@@ -1707,14 +1564,10 @@
       <c r="G38" s="2">
         <v>9843</v>
       </c>
-      <c r="H38" s="12"/>
-      <c r="I38" s="12"/>
-      <c r="J38" s="12"/>
-      <c r="K38" s="12"/>
       <c r="L38" s="12"/>
-      <c r="N38" s="21"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N38" s="20"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" s="9">
         <v>36557</v>
       </c>
@@ -1737,14 +1590,10 @@
       <c r="G39" s="2">
         <v>10017</v>
       </c>
-      <c r="H39" s="12"/>
-      <c r="I39" s="12"/>
-      <c r="J39" s="12"/>
-      <c r="K39" s="12"/>
       <c r="L39" s="12"/>
-      <c r="N39" s="21"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N39" s="20"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" s="9">
         <v>36586</v>
       </c>
@@ -1767,14 +1616,10 @@
       <c r="G40" s="2">
         <v>10295</v>
       </c>
-      <c r="H40" s="12"/>
-      <c r="I40" s="12"/>
-      <c r="J40" s="12"/>
-      <c r="K40" s="12"/>
       <c r="L40" s="12"/>
-      <c r="N40" s="21"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N40" s="20"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" s="9">
         <v>36617</v>
       </c>
@@ -1797,14 +1642,10 @@
       <c r="G41" s="2">
         <v>10183</v>
       </c>
-      <c r="H41" s="12"/>
-      <c r="I41" s="12"/>
-      <c r="J41" s="12"/>
-      <c r="K41" s="12"/>
       <c r="L41" s="12"/>
-      <c r="N41" s="21"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N41" s="20"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" s="9">
         <v>36647</v>
       </c>
@@ -1827,14 +1668,10 @@
       <c r="G42" s="2">
         <v>10225</v>
       </c>
-      <c r="H42" s="12"/>
-      <c r="I42" s="12"/>
-      <c r="J42" s="12"/>
-      <c r="K42" s="12"/>
       <c r="L42" s="12"/>
-      <c r="N42" s="21"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N42" s="20"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43" s="9">
         <v>36678</v>
       </c>
@@ -1857,14 +1694,10 @@
       <c r="G43" s="2">
         <v>10308</v>
       </c>
-      <c r="H43" s="12"/>
-      <c r="I43" s="12"/>
-      <c r="J43" s="12"/>
-      <c r="K43" s="12"/>
       <c r="L43" s="12"/>
-      <c r="N43" s="21"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N43" s="20"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" s="9">
         <v>36708</v>
       </c>
@@ -1887,14 +1720,10 @@
       <c r="G44" s="2">
         <v>10258</v>
       </c>
-      <c r="H44" s="12"/>
-      <c r="I44" s="12"/>
-      <c r="J44" s="12"/>
-      <c r="K44" s="12"/>
       <c r="L44" s="12"/>
-      <c r="N44" s="21"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N44" s="20"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" s="9">
         <v>36739</v>
       </c>
@@ -1917,14 +1746,10 @@
       <c r="G45" s="2">
         <v>10252</v>
       </c>
-      <c r="H45" s="12"/>
-      <c r="I45" s="12"/>
-      <c r="J45" s="12"/>
-      <c r="K45" s="12"/>
       <c r="L45" s="12"/>
-      <c r="N45" s="21"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N45" s="20"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" s="9">
         <v>36770</v>
       </c>
@@ -1947,14 +1772,10 @@
       <c r="G46" s="2">
         <v>10205</v>
       </c>
-      <c r="H46" s="12"/>
-      <c r="I46" s="12"/>
-      <c r="J46" s="12"/>
-      <c r="K46" s="12"/>
       <c r="L46" s="12"/>
-      <c r="N46" s="21"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N46" s="20"/>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" s="9">
         <v>36800</v>
       </c>
@@ -1977,14 +1798,10 @@
       <c r="G47" s="2">
         <v>9962</v>
       </c>
-      <c r="H47" s="12"/>
-      <c r="I47" s="12"/>
-      <c r="J47" s="12"/>
-      <c r="K47" s="12"/>
       <c r="L47" s="12"/>
-      <c r="N47" s="21"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N47" s="20"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" s="9">
         <v>36831</v>
       </c>
@@ -2007,14 +1824,10 @@
       <c r="G48" s="2">
         <v>9870</v>
       </c>
-      <c r="H48" s="12"/>
-      <c r="I48" s="12"/>
-      <c r="J48" s="12"/>
-      <c r="K48" s="12"/>
       <c r="L48" s="12"/>
-      <c r="N48" s="21"/>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N48" s="20"/>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" s="9">
         <v>36861</v>
       </c>
@@ -2037,14 +1850,10 @@
       <c r="G49" s="2">
         <v>9957</v>
       </c>
-      <c r="H49" s="12"/>
-      <c r="I49" s="12"/>
-      <c r="J49" s="12"/>
-      <c r="K49" s="12"/>
       <c r="L49" s="12"/>
-      <c r="N49" s="21"/>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N49" s="20"/>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50" s="9">
         <v>36892</v>
       </c>
@@ -2067,14 +1876,10 @@
       <c r="G50" s="2">
         <v>10114</v>
       </c>
-      <c r="H50" s="12"/>
-      <c r="I50" s="12"/>
-      <c r="J50" s="12"/>
-      <c r="K50" s="12"/>
       <c r="L50" s="12"/>
-      <c r="N50" s="21"/>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="20"/>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A51" s="9">
         <v>36923</v>
       </c>
@@ -2097,14 +1902,10 @@
       <c r="G51" s="2">
         <v>10268</v>
       </c>
-      <c r="H51" s="12"/>
-      <c r="I51" s="12"/>
-      <c r="J51" s="12"/>
-      <c r="K51" s="12"/>
       <c r="L51" s="12"/>
-      <c r="N51" s="21"/>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="20"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" s="9">
         <v>36951</v>
       </c>
@@ -2127,14 +1928,10 @@
       <c r="G52" s="2">
         <v>10413</v>
       </c>
-      <c r="H52" s="12"/>
-      <c r="I52" s="12"/>
-      <c r="J52" s="12"/>
-      <c r="K52" s="12"/>
       <c r="L52" s="12"/>
-      <c r="N52" s="21"/>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N52" s="20"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A53" s="9">
         <v>36982</v>
       </c>
@@ -2157,14 +1954,10 @@
       <c r="G53" s="2">
         <v>10289</v>
       </c>
-      <c r="H53" s="12"/>
-      <c r="I53" s="12"/>
-      <c r="J53" s="12"/>
-      <c r="K53" s="12"/>
       <c r="L53" s="12"/>
-      <c r="N53" s="21"/>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="20"/>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A54" s="9">
         <v>37012</v>
       </c>
@@ -2187,14 +1980,10 @@
       <c r="G54" s="2">
         <v>10272</v>
       </c>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
-      <c r="K54" s="12"/>
       <c r="L54" s="12"/>
-      <c r="N54" s="21"/>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N54" s="20"/>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A55" s="9">
         <v>37043</v>
       </c>
@@ -2217,14 +2006,10 @@
       <c r="G55" s="2">
         <v>10232</v>
       </c>
-      <c r="H55" s="12"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="12"/>
-      <c r="K55" s="12"/>
       <c r="L55" s="12"/>
-      <c r="N55" s="21"/>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N55" s="20"/>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A56" s="9">
         <v>37073</v>
       </c>
@@ -2247,14 +2032,10 @@
       <c r="G56" s="2">
         <v>10153</v>
       </c>
-      <c r="H56" s="12"/>
-      <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
-      <c r="K56" s="12"/>
       <c r="L56" s="12"/>
-      <c r="N56" s="21"/>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N56" s="20"/>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A57" s="9">
         <v>37104</v>
       </c>
@@ -2277,14 +2058,10 @@
       <c r="G57" s="2">
         <v>10218</v>
       </c>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12"/>
-      <c r="K57" s="12"/>
       <c r="L57" s="12"/>
-      <c r="N57" s="21"/>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N57" s="20"/>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A58" s="9">
         <v>37135</v>
       </c>
@@ -2307,14 +2084,10 @@
       <c r="G58" s="2">
         <v>9992</v>
       </c>
-      <c r="H58" s="12"/>
-      <c r="I58" s="12"/>
-      <c r="J58" s="12"/>
-      <c r="K58" s="12"/>
       <c r="L58" s="12"/>
-      <c r="N58" s="21"/>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N58" s="20"/>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A59" s="9">
         <v>37165</v>
       </c>
@@ -2337,14 +2110,10 @@
       <c r="G59" s="2">
         <v>9646</v>
       </c>
-      <c r="H59" s="12"/>
-      <c r="I59" s="12"/>
-      <c r="J59" s="12"/>
-      <c r="K59" s="12"/>
       <c r="L59" s="12"/>
-      <c r="N59" s="21"/>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N59" s="20"/>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60" s="9">
         <v>37196</v>
       </c>
@@ -2367,14 +2136,10 @@
       <c r="G60" s="2">
         <v>9642</v>
       </c>
-      <c r="H60" s="12"/>
-      <c r="I60" s="12"/>
-      <c r="J60" s="12"/>
-      <c r="K60" s="12"/>
       <c r="L60" s="12"/>
-      <c r="N60" s="21"/>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N60" s="20"/>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A61" s="9">
         <v>37226</v>
       </c>
@@ -2397,14 +2162,10 @@
       <c r="G61" s="2">
         <v>9843</v>
       </c>
-      <c r="H61" s="12"/>
-      <c r="I61" s="12"/>
-      <c r="J61" s="12"/>
-      <c r="K61" s="12"/>
       <c r="L61" s="12"/>
-      <c r="N61" s="21"/>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N61" s="20"/>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A62" s="9">
         <v>37258</v>
       </c>
@@ -2427,14 +2188,10 @@
       <c r="G62" s="2">
         <v>10127</v>
       </c>
-      <c r="H62" s="12"/>
-      <c r="I62" s="12"/>
-      <c r="J62" s="12"/>
-      <c r="K62" s="12"/>
       <c r="L62" s="12"/>
-      <c r="N62" s="21"/>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N62" s="20"/>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A63" s="9">
         <v>37288</v>
       </c>
@@ -2457,14 +2214,10 @@
       <c r="G63" s="2">
         <v>10380</v>
       </c>
-      <c r="H63" s="12"/>
-      <c r="I63" s="12"/>
-      <c r="J63" s="12"/>
-      <c r="K63" s="12"/>
       <c r="L63" s="12"/>
-      <c r="N63" s="21"/>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="20"/>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A64" s="9">
         <v>37316</v>
       </c>
@@ -2487,14 +2240,10 @@
       <c r="G64" s="2">
         <v>10501</v>
       </c>
-      <c r="H64" s="12"/>
-      <c r="I64" s="12"/>
-      <c r="J64" s="12"/>
-      <c r="K64" s="12"/>
       <c r="L64" s="12"/>
-      <c r="N64" s="21"/>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="20"/>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A65" s="9">
         <v>37347</v>
       </c>
@@ -2517,14 +2266,10 @@
       <c r="G65" s="2">
         <v>10366</v>
       </c>
-      <c r="H65" s="12"/>
-      <c r="I65" s="12"/>
-      <c r="J65" s="12"/>
-      <c r="K65" s="12"/>
       <c r="L65" s="12"/>
-      <c r="N65" s="21"/>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="20"/>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A66" s="9">
         <v>37377</v>
       </c>
@@ -2547,14 +2292,10 @@
       <c r="G66" s="2">
         <v>10329</v>
       </c>
-      <c r="H66" s="12"/>
-      <c r="I66" s="12"/>
-      <c r="J66" s="12"/>
-      <c r="K66" s="12"/>
       <c r="L66" s="12"/>
-      <c r="N66" s="21"/>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N66" s="20"/>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67" s="9">
         <v>37408</v>
       </c>
@@ -2592,14 +2333,10 @@
       <c r="G67" s="2">
         <v>10187</v>
       </c>
-      <c r="H67" s="12"/>
-      <c r="I67" s="12"/>
-      <c r="J67" s="12"/>
-      <c r="K67" s="12"/>
       <c r="L67" s="12"/>
-      <c r="N67" s="21"/>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N67" s="20"/>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A68" s="9">
         <v>37438</v>
       </c>
@@ -2622,14 +2359,10 @@
       <c r="G68" s="2">
         <v>10059</v>
       </c>
-      <c r="H68" s="12"/>
-      <c r="I68" s="12"/>
-      <c r="J68" s="12"/>
-      <c r="K68" s="12"/>
       <c r="L68" s="12"/>
-      <c r="N68" s="21"/>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="20"/>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A69" s="9">
         <v>37469</v>
       </c>
@@ -2652,14 +2385,10 @@
       <c r="G69" s="2">
         <v>9908</v>
       </c>
-      <c r="H69" s="12"/>
-      <c r="I69" s="12"/>
-      <c r="J69" s="12"/>
-      <c r="K69" s="12"/>
       <c r="L69" s="12"/>
-      <c r="N69" s="21"/>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="20"/>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A70" s="9">
         <v>37500</v>
       </c>
@@ -2682,14 +2411,10 @@
       <c r="G70" s="2">
         <v>9752</v>
       </c>
-      <c r="H70" s="12"/>
-      <c r="I70" s="12"/>
-      <c r="J70" s="12"/>
-      <c r="K70" s="12"/>
       <c r="L70" s="12"/>
-      <c r="N70" s="21"/>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="20"/>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A71" s="9">
         <v>37530</v>
       </c>
@@ -2712,14 +2437,10 @@
       <c r="G71" s="2">
         <v>9399</v>
       </c>
-      <c r="H71" s="12"/>
-      <c r="I71" s="12"/>
-      <c r="J71" s="12"/>
-      <c r="K71" s="12"/>
       <c r="L71" s="12"/>
-      <c r="N71" s="21"/>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="20"/>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A72" s="9">
         <v>37561</v>
       </c>
@@ -2742,14 +2463,10 @@
       <c r="G72" s="2">
         <v>9366</v>
       </c>
-      <c r="H72" s="12"/>
-      <c r="I72" s="12"/>
-      <c r="J72" s="12"/>
-      <c r="K72" s="12"/>
       <c r="L72" s="12"/>
-      <c r="N72" s="21"/>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N72" s="20"/>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A73" s="9">
         <v>37591</v>
       </c>
@@ -2772,14 +2489,10 @@
       <c r="G73" s="2">
         <v>9478</v>
       </c>
-      <c r="H73" s="12"/>
-      <c r="I73" s="12"/>
-      <c r="J73" s="12"/>
-      <c r="K73" s="12"/>
       <c r="L73" s="12"/>
-      <c r="N73" s="21"/>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="20"/>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A74" s="9">
         <v>37622</v>
       </c>
@@ -2802,14 +2515,10 @@
       <c r="G74" s="2">
         <v>9533</v>
       </c>
-      <c r="H74" s="12"/>
-      <c r="I74" s="12"/>
-      <c r="J74" s="12"/>
-      <c r="K74" s="12"/>
       <c r="L74" s="12"/>
-      <c r="N74" s="21"/>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="20"/>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A75" s="9">
         <v>37653</v>
       </c>
@@ -2832,14 +2541,10 @@
       <c r="G75" s="2">
         <v>9591</v>
       </c>
-      <c r="H75" s="12"/>
-      <c r="I75" s="12"/>
-      <c r="J75" s="12"/>
-      <c r="K75" s="12"/>
       <c r="L75" s="12"/>
-      <c r="N75" s="21"/>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="20"/>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A76" s="9">
         <v>37681</v>
       </c>
@@ -2862,14 +2567,10 @@
       <c r="G76" s="2">
         <v>9662</v>
       </c>
-      <c r="H76" s="12"/>
-      <c r="I76" s="12"/>
-      <c r="J76" s="12"/>
-      <c r="K76" s="12"/>
       <c r="L76" s="12"/>
-      <c r="N76" s="21"/>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N76" s="20"/>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A77" s="9">
         <v>37712</v>
       </c>
@@ -2892,14 +2593,10 @@
       <c r="G77" s="2">
         <v>9612</v>
       </c>
-      <c r="H77" s="12"/>
-      <c r="I77" s="12"/>
-      <c r="J77" s="12"/>
-      <c r="K77" s="12"/>
       <c r="L77" s="12"/>
-      <c r="N77" s="21"/>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="20"/>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A78" s="9">
         <v>37742</v>
       </c>
@@ -2922,14 +2619,10 @@
       <c r="G78" s="2">
         <v>9721</v>
       </c>
-      <c r="H78" s="12"/>
-      <c r="I78" s="12"/>
-      <c r="J78" s="12"/>
-      <c r="K78" s="12"/>
       <c r="L78" s="12"/>
-      <c r="N78" s="21"/>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N78" s="20"/>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A79" s="9">
         <v>37773</v>
       </c>
@@ -2952,14 +2645,10 @@
       <c r="G79" s="2">
         <v>9887</v>
       </c>
-      <c r="H79" s="12"/>
-      <c r="I79" s="12"/>
-      <c r="J79" s="12"/>
-      <c r="K79" s="12"/>
       <c r="L79" s="12"/>
-      <c r="N79" s="21"/>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N79" s="20"/>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A80" s="9">
         <v>37803</v>
       </c>
@@ -2982,14 +2671,10 @@
       <c r="G80" s="2">
         <v>9940</v>
       </c>
-      <c r="H80" s="12"/>
-      <c r="I80" s="12"/>
-      <c r="J80" s="12"/>
-      <c r="K80" s="12"/>
       <c r="L80" s="12"/>
-      <c r="N80" s="21"/>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N80" s="20"/>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A81" s="9">
         <v>37834</v>
       </c>
@@ -3012,14 +2697,10 @@
       <c r="G81" s="2">
         <v>9995</v>
       </c>
-      <c r="H81" s="12"/>
-      <c r="I81" s="12"/>
-      <c r="J81" s="12"/>
-      <c r="K81" s="12"/>
       <c r="L81" s="12"/>
-      <c r="N81" s="21"/>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N81" s="20"/>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A82" s="9">
         <v>37865</v>
       </c>
@@ -3042,14 +2723,10 @@
       <c r="G82" s="2">
         <v>9975</v>
       </c>
-      <c r="H82" s="12"/>
-      <c r="I82" s="12"/>
-      <c r="J82" s="12"/>
-      <c r="K82" s="12"/>
       <c r="L82" s="12"/>
-      <c r="N82" s="21"/>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N82" s="20"/>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A83" s="9">
         <v>37895</v>
       </c>
@@ -3072,14 +2749,10 @@
       <c r="G83" s="2">
         <v>9838</v>
       </c>
-      <c r="H83" s="12"/>
-      <c r="I83" s="12"/>
-      <c r="J83" s="12"/>
-      <c r="K83" s="12"/>
       <c r="L83" s="12"/>
-      <c r="N83" s="21"/>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N83" s="20"/>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A84" s="9">
         <v>37926</v>
       </c>
@@ -3102,14 +2775,10 @@
       <c r="G84" s="2">
         <v>9747</v>
       </c>
-      <c r="H84" s="12"/>
-      <c r="I84" s="12"/>
-      <c r="J84" s="12"/>
-      <c r="K84" s="12"/>
       <c r="L84" s="12"/>
-      <c r="N84" s="21"/>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="20"/>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A85" s="9">
         <v>37956</v>
       </c>
@@ -3132,14 +2801,10 @@
       <c r="G85" s="2">
         <v>9754</v>
       </c>
-      <c r="H85" s="12"/>
-      <c r="I85" s="12"/>
-      <c r="J85" s="12"/>
-      <c r="K85" s="12"/>
       <c r="L85" s="12"/>
-      <c r="N85" s="21"/>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="20"/>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A86" s="9">
         <v>37987</v>
       </c>
@@ -3162,14 +2827,10 @@
       <c r="G86" s="2">
         <v>9834</v>
       </c>
-      <c r="H86" s="12"/>
-      <c r="I86" s="12"/>
-      <c r="J86" s="12"/>
-      <c r="K86" s="12"/>
       <c r="L86" s="12"/>
-      <c r="N86" s="21"/>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="20"/>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A87" s="9">
         <v>38018</v>
       </c>
@@ -3192,14 +2853,10 @@
       <c r="G87" s="2">
         <v>10057</v>
       </c>
-      <c r="H87" s="12"/>
-      <c r="I87" s="12"/>
-      <c r="J87" s="12"/>
-      <c r="K87" s="12"/>
       <c r="L87" s="12"/>
-      <c r="N87" s="21"/>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="20"/>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A88" s="9">
         <v>38047</v>
       </c>
@@ -3222,14 +2879,10 @@
       <c r="G88" s="2">
         <v>10431</v>
       </c>
-      <c r="H88" s="12"/>
-      <c r="I88" s="12"/>
-      <c r="J88" s="12"/>
-      <c r="K88" s="12"/>
       <c r="L88" s="12"/>
-      <c r="N88" s="21"/>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="20"/>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A89" s="9">
         <v>38078</v>
       </c>
@@ -3252,14 +2905,10 @@
       <c r="G89" s="2">
         <v>10445</v>
       </c>
-      <c r="H89" s="12"/>
-      <c r="I89" s="12"/>
-      <c r="J89" s="12"/>
-      <c r="K89" s="12"/>
       <c r="L89" s="12"/>
-      <c r="N89" s="21"/>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N89" s="20"/>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A90" s="9">
         <v>38108</v>
       </c>
@@ -3282,14 +2931,10 @@
       <c r="G90" s="2">
         <v>10450</v>
       </c>
-      <c r="H90" s="12"/>
-      <c r="I90" s="12"/>
-      <c r="J90" s="12"/>
-      <c r="K90" s="12"/>
       <c r="L90" s="12"/>
-      <c r="N90" s="21"/>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N90" s="20"/>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A91" s="9">
         <v>38139</v>
       </c>
@@ -3312,14 +2957,10 @@
       <c r="G91" s="2">
         <v>10328</v>
       </c>
-      <c r="H91" s="12"/>
-      <c r="I91" s="12"/>
-      <c r="J91" s="12"/>
-      <c r="K91" s="12"/>
       <c r="L91" s="12"/>
-      <c r="N91" s="21"/>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N91" s="20"/>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A92" s="9">
         <v>38169</v>
       </c>
@@ -3342,14 +2983,10 @@
       <c r="G92" s="2">
         <v>10263</v>
       </c>
-      <c r="H92" s="12"/>
-      <c r="I92" s="12"/>
-      <c r="J92" s="12"/>
-      <c r="K92" s="12"/>
       <c r="L92" s="12"/>
-      <c r="N92" s="21"/>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="20"/>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A93" s="9">
         <v>38200</v>
       </c>
@@ -3372,14 +3009,10 @@
       <c r="G93" s="2">
         <v>10203</v>
       </c>
-      <c r="H93" s="12"/>
-      <c r="I93" s="12"/>
-      <c r="J93" s="12"/>
-      <c r="K93" s="12"/>
       <c r="L93" s="12"/>
-      <c r="N93" s="21"/>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="20"/>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A94" s="9">
         <v>38231</v>
       </c>
@@ -3402,14 +3035,10 @@
       <c r="G94" s="2">
         <v>10076</v>
       </c>
-      <c r="H94" s="12"/>
-      <c r="I94" s="12"/>
-      <c r="J94" s="12"/>
-      <c r="K94" s="12"/>
       <c r="L94" s="12"/>
-      <c r="N94" s="21"/>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N94" s="20"/>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A95" s="9">
         <v>38261</v>
       </c>
@@ -3432,14 +3061,10 @@
       <c r="G95" s="2">
         <v>9898</v>
       </c>
-      <c r="H95" s="12"/>
-      <c r="I95" s="12"/>
-      <c r="J95" s="12"/>
-      <c r="K95" s="12"/>
       <c r="L95" s="12"/>
-      <c r="N95" s="21"/>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N95" s="20"/>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A96" s="9">
         <v>38292</v>
       </c>
@@ -3462,14 +3087,10 @@
       <c r="G96" s="2">
         <v>9898</v>
       </c>
-      <c r="H96" s="12"/>
-      <c r="I96" s="12"/>
-      <c r="J96" s="12"/>
-      <c r="K96" s="12"/>
       <c r="L96" s="12"/>
-      <c r="N96" s="21"/>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N96" s="20"/>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A97" s="9">
         <v>38322</v>
       </c>
@@ -3492,14 +3113,10 @@
       <c r="G97" s="2">
         <v>10062</v>
       </c>
-      <c r="H97" s="12"/>
-      <c r="I97" s="12"/>
-      <c r="J97" s="12"/>
-      <c r="K97" s="12"/>
       <c r="L97" s="12"/>
-      <c r="N97" s="21"/>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="20"/>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A98" s="9">
         <v>38353</v>
       </c>
@@ -3522,14 +3139,10 @@
       <c r="G98" s="2">
         <v>10273</v>
       </c>
-      <c r="H98" s="12"/>
-      <c r="I98" s="12"/>
-      <c r="J98" s="12"/>
-      <c r="K98" s="12"/>
       <c r="L98" s="12"/>
-      <c r="N98" s="21"/>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="20"/>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A99" s="9">
         <v>38384</v>
       </c>
@@ -3552,14 +3165,10 @@
       <c r="G99" s="2">
         <v>10609</v>
       </c>
-      <c r="H99" s="12"/>
-      <c r="I99" s="12"/>
-      <c r="J99" s="12"/>
-      <c r="K99" s="12"/>
       <c r="L99" s="12"/>
-      <c r="N99" s="21"/>
-    </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="20"/>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A100" s="9">
         <v>38412</v>
       </c>
@@ -3582,14 +3191,10 @@
       <c r="G100" s="2">
         <v>10992</v>
       </c>
-      <c r="H100" s="12"/>
-      <c r="I100" s="12"/>
-      <c r="J100" s="12"/>
-      <c r="K100" s="12"/>
       <c r="L100" s="12"/>
-      <c r="N100" s="21"/>
-    </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N100" s="20"/>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A101" s="9">
         <v>38443</v>
       </c>
@@ -3612,14 +3217,10 @@
       <c r="G101" s="2">
         <v>10949</v>
       </c>
-      <c r="H101" s="12"/>
-      <c r="I101" s="12"/>
-      <c r="J101" s="12"/>
-      <c r="K101" s="12"/>
       <c r="L101" s="12"/>
-      <c r="N101" s="21"/>
-    </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N101" s="20"/>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A102" s="9">
         <v>38473</v>
       </c>
@@ -3642,14 +3243,10 @@
       <c r="G102" s="2">
         <v>10822</v>
       </c>
-      <c r="H102" s="12"/>
-      <c r="I102" s="12"/>
-      <c r="J102" s="12"/>
-      <c r="K102" s="12"/>
       <c r="L102" s="12"/>
-      <c r="N102" s="21"/>
-    </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N102" s="20"/>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A103" s="9">
         <v>38504</v>
       </c>
@@ -3672,14 +3269,10 @@
       <c r="G103" s="2">
         <v>10658</v>
       </c>
-      <c r="H103" s="12"/>
-      <c r="I103" s="12"/>
-      <c r="J103" s="12"/>
-      <c r="K103" s="12"/>
       <c r="L103" s="12"/>
-      <c r="N103" s="21"/>
-    </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N103" s="20"/>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A104" s="9">
         <v>38534</v>
       </c>
@@ -3702,14 +3295,10 @@
       <c r="G104" s="2">
         <v>10448</v>
       </c>
-      <c r="H104" s="12"/>
-      <c r="I104" s="12"/>
-      <c r="J104" s="12"/>
-      <c r="K104" s="12"/>
       <c r="L104" s="12"/>
-      <c r="N104" s="21"/>
-    </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N104" s="20"/>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A105" s="9">
         <v>38565</v>
       </c>
@@ -3732,14 +3321,10 @@
       <c r="G105" s="2">
         <v>10429</v>
       </c>
-      <c r="H105" s="12"/>
-      <c r="I105" s="12"/>
-      <c r="J105" s="12"/>
-      <c r="K105" s="12"/>
       <c r="L105" s="12"/>
-      <c r="N105" s="21"/>
-    </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N105" s="20"/>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A106" s="9">
         <v>38596</v>
       </c>
@@ -3762,14 +3347,10 @@
       <c r="G106" s="2">
         <v>10424</v>
       </c>
-      <c r="H106" s="12"/>
-      <c r="I106" s="12"/>
-      <c r="J106" s="12"/>
-      <c r="K106" s="12"/>
       <c r="L106" s="12"/>
-      <c r="N106" s="21"/>
-    </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N106" s="20"/>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A107" s="9">
         <v>38626</v>
       </c>
@@ -3792,14 +3373,10 @@
       <c r="G107" s="2">
         <v>10358</v>
       </c>
-      <c r="H107" s="12"/>
-      <c r="I107" s="12"/>
-      <c r="J107" s="12"/>
-      <c r="K107" s="12"/>
       <c r="L107" s="12"/>
-      <c r="N107" s="21"/>
-    </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N107" s="20"/>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A108" s="9">
         <v>38657</v>
       </c>
@@ -3822,14 +3399,10 @@
       <c r="G108" s="2">
         <v>10497</v>
       </c>
-      <c r="H108" s="12"/>
-      <c r="I108" s="12"/>
-      <c r="J108" s="12"/>
-      <c r="K108" s="12"/>
       <c r="L108" s="12"/>
-      <c r="N108" s="21"/>
-    </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N108" s="20"/>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A109" s="9">
         <v>38687</v>
       </c>
@@ -3852,14 +3425,10 @@
       <c r="G109" s="2">
         <v>10715</v>
       </c>
-      <c r="H109" s="12"/>
-      <c r="I109" s="12"/>
-      <c r="J109" s="12"/>
-      <c r="K109" s="12"/>
       <c r="L109" s="12"/>
-      <c r="N109" s="21"/>
-    </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N109" s="20"/>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A110" s="9">
         <v>38718</v>
       </c>
@@ -3882,14 +3451,10 @@
       <c r="G110" s="2">
         <v>10825</v>
       </c>
-      <c r="H110" s="12"/>
-      <c r="I110" s="12"/>
-      <c r="J110" s="12"/>
-      <c r="K110" s="12"/>
       <c r="L110" s="12"/>
-      <c r="N110" s="21"/>
-    </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N110" s="20"/>
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A111" s="9">
         <v>38749</v>
       </c>
@@ -3912,14 +3477,10 @@
       <c r="G111" s="2">
         <v>10969</v>
       </c>
-      <c r="H111" s="12"/>
-      <c r="I111" s="12"/>
-      <c r="J111" s="12"/>
-      <c r="K111" s="12"/>
       <c r="L111" s="12"/>
-      <c r="N111" s="21"/>
-    </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N111" s="20"/>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A112" s="9">
         <v>38777</v>
       </c>
@@ -3942,14 +3503,10 @@
       <c r="G112" s="2">
         <v>11174</v>
       </c>
-      <c r="H112" s="12"/>
-      <c r="I112" s="12"/>
-      <c r="J112" s="12"/>
-      <c r="K112" s="12"/>
       <c r="L112" s="12"/>
-      <c r="N112" s="21"/>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N112" s="20"/>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A113" s="9">
         <v>38808</v>
       </c>
@@ -3972,14 +3529,10 @@
       <c r="G113" s="2">
         <v>11048</v>
       </c>
-      <c r="H113" s="12"/>
-      <c r="I113" s="12"/>
-      <c r="J113" s="12"/>
-      <c r="K113" s="12"/>
       <c r="L113" s="12"/>
-      <c r="N113" s="21"/>
-    </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N113" s="20"/>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A114" s="9">
         <v>38838</v>
       </c>
@@ -4002,14 +3555,10 @@
       <c r="G114" s="2">
         <v>10873</v>
       </c>
-      <c r="H114" s="12"/>
-      <c r="I114" s="12"/>
-      <c r="J114" s="12"/>
-      <c r="K114" s="12"/>
       <c r="L114" s="12"/>
-      <c r="N114" s="21"/>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N114" s="20"/>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A115" s="9">
         <v>38869</v>
       </c>
@@ -4032,14 +3581,10 @@
       <c r="G115" s="2">
         <v>10807</v>
       </c>
-      <c r="H115" s="12"/>
-      <c r="I115" s="12"/>
-      <c r="J115" s="12"/>
-      <c r="K115" s="12"/>
       <c r="L115" s="12"/>
-      <c r="N115" s="21"/>
-    </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N115" s="20"/>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A116" s="9">
         <v>38899</v>
       </c>
@@ -4062,14 +3607,10 @@
       <c r="G116" s="2">
         <v>10645</v>
       </c>
-      <c r="H116" s="12"/>
-      <c r="I116" s="12"/>
-      <c r="J116" s="12"/>
-      <c r="K116" s="12"/>
       <c r="L116" s="12"/>
-      <c r="N116" s="21"/>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N116" s="20"/>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A117" s="9">
         <v>38930</v>
       </c>
@@ -4092,14 +3633,10 @@
       <c r="G117" s="2">
         <v>10651</v>
       </c>
-      <c r="H117" s="12"/>
-      <c r="I117" s="12"/>
-      <c r="J117" s="12"/>
-      <c r="K117" s="12"/>
       <c r="L117" s="12"/>
-      <c r="N117" s="21"/>
-    </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N117" s="20"/>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A118" s="9">
         <v>38961</v>
       </c>
@@ -4122,14 +3659,10 @@
       <c r="G118" s="2">
         <v>10505</v>
       </c>
-      <c r="H118" s="12"/>
-      <c r="I118" s="12"/>
-      <c r="J118" s="12"/>
-      <c r="K118" s="12"/>
       <c r="L118" s="12"/>
-      <c r="N118" s="21"/>
-    </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N118" s="20"/>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A119" s="9">
         <v>38991</v>
       </c>
@@ -4152,14 +3685,10 @@
       <c r="G119" s="2">
         <v>10391</v>
       </c>
-      <c r="H119" s="12"/>
-      <c r="I119" s="12"/>
-      <c r="J119" s="12"/>
-      <c r="K119" s="12"/>
       <c r="L119" s="12"/>
-      <c r="N119" s="21"/>
-    </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N119" s="20"/>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A120" s="9">
         <v>39022</v>
       </c>
@@ -4182,14 +3711,10 @@
       <c r="G120" s="2">
         <v>10529</v>
       </c>
-      <c r="H120" s="12"/>
-      <c r="I120" s="12"/>
-      <c r="J120" s="12"/>
-      <c r="K120" s="12"/>
       <c r="L120" s="12"/>
-      <c r="N120" s="21"/>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N120" s="20"/>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A121" s="9">
         <v>39052</v>
       </c>
@@ -4212,14 +3737,10 @@
       <c r="G121" s="2">
         <v>10691</v>
       </c>
-      <c r="H121" s="12"/>
-      <c r="I121" s="12"/>
-      <c r="J121" s="12"/>
-      <c r="K121" s="12"/>
       <c r="L121" s="12"/>
-      <c r="N121" s="21"/>
-    </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N121" s="20"/>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A122" s="9">
         <v>39083</v>
       </c>
@@ -4242,14 +3763,10 @@
       <c r="G122" s="2">
         <v>10777</v>
       </c>
-      <c r="H122" s="12"/>
-      <c r="I122" s="12"/>
-      <c r="J122" s="12"/>
-      <c r="K122" s="12"/>
       <c r="L122" s="12"/>
-      <c r="N122" s="21"/>
-    </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N122" s="20"/>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A123" s="9">
         <v>39114</v>
       </c>
@@ -4272,14 +3789,10 @@
       <c r="G123" s="2">
         <v>11029</v>
       </c>
-      <c r="H123" s="12"/>
-      <c r="I123" s="12"/>
-      <c r="J123" s="12"/>
-      <c r="K123" s="12"/>
       <c r="L123" s="12"/>
-      <c r="N123" s="21"/>
-    </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N123" s="20"/>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A124" s="9">
         <v>39142</v>
       </c>
@@ -4302,14 +3815,10 @@
       <c r="G124" s="2">
         <v>11434</v>
       </c>
-      <c r="H124" s="12"/>
-      <c r="I124" s="12"/>
-      <c r="J124" s="12"/>
-      <c r="K124" s="12"/>
       <c r="L124" s="12"/>
-      <c r="N124" s="21"/>
-    </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N124" s="20"/>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A125" s="9">
         <v>39173</v>
       </c>
@@ -4332,14 +3841,10 @@
       <c r="G125" s="2">
         <v>11389</v>
       </c>
-      <c r="H125" s="12"/>
-      <c r="I125" s="12"/>
-      <c r="J125" s="12"/>
-      <c r="K125" s="12"/>
       <c r="L125" s="12"/>
-      <c r="N125" s="21"/>
-    </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N125" s="20"/>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A126" s="9">
         <v>39203</v>
       </c>
@@ -4362,14 +3867,10 @@
       <c r="G126" s="2">
         <v>11322</v>
       </c>
-      <c r="H126" s="12"/>
-      <c r="I126" s="12"/>
-      <c r="J126" s="12"/>
-      <c r="K126" s="12"/>
       <c r="L126" s="12"/>
-      <c r="N126" s="21"/>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N126" s="20"/>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A127" s="9">
         <v>39234</v>
       </c>
@@ -4392,14 +3893,10 @@
       <c r="G127" s="2">
         <v>11218</v>
       </c>
-      <c r="H127" s="12"/>
-      <c r="I127" s="12"/>
-      <c r="J127" s="12"/>
-      <c r="K127" s="12"/>
       <c r="L127" s="12"/>
-      <c r="N127" s="21"/>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N127" s="20"/>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A128" s="9">
         <v>39264</v>
       </c>
@@ -4422,14 +3919,10 @@
       <c r="G128" s="2">
         <v>11076</v>
       </c>
-      <c r="H128" s="12"/>
-      <c r="I128" s="12"/>
-      <c r="J128" s="12"/>
-      <c r="K128" s="12"/>
       <c r="L128" s="12"/>
-      <c r="N128" s="21"/>
-    </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N128" s="20"/>
+    </row>
+    <row r="129" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A129" s="9">
         <v>39295</v>
       </c>
@@ -4452,14 +3945,10 @@
       <c r="G129" s="2">
         <v>11129</v>
       </c>
-      <c r="H129" s="12"/>
-      <c r="I129" s="12"/>
-      <c r="J129" s="12"/>
-      <c r="K129" s="12"/>
       <c r="L129" s="12"/>
-      <c r="N129" s="21"/>
-    </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N129" s="20"/>
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A130" s="9">
         <v>39326</v>
       </c>
@@ -4482,14 +3971,10 @@
       <c r="G130" s="2">
         <v>11093</v>
       </c>
-      <c r="H130" s="12"/>
-      <c r="I130" s="12"/>
-      <c r="J130" s="12"/>
-      <c r="K130" s="12"/>
       <c r="L130" s="12"/>
-      <c r="N130" s="21"/>
-    </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N130" s="20"/>
+    </row>
+    <row r="131" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A131" s="9">
         <v>39356</v>
       </c>
@@ -4527,14 +4012,10 @@
       <c r="G131" s="2">
         <v>10775</v>
       </c>
-      <c r="H131" s="12"/>
-      <c r="I131" s="12"/>
-      <c r="J131" s="12"/>
-      <c r="K131" s="12"/>
       <c r="L131" s="12"/>
-      <c r="N131" s="21"/>
-    </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N131" s="20"/>
+    </row>
+    <row r="132" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A132" s="9">
         <v>39387</v>
       </c>
@@ -4557,14 +4038,10 @@
       <c r="G132" s="2">
         <v>10643</v>
       </c>
-      <c r="H132" s="12"/>
-      <c r="I132" s="12"/>
-      <c r="J132" s="12"/>
-      <c r="K132" s="12"/>
       <c r="L132" s="12"/>
-      <c r="N132" s="21"/>
-    </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N132" s="20"/>
+    </row>
+    <row r="133" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A133" s="9">
         <v>39417</v>
       </c>
@@ -4587,14 +4064,10 @@
       <c r="G133" s="2">
         <v>10559</v>
       </c>
-      <c r="H133" s="12"/>
-      <c r="I133" s="12"/>
-      <c r="J133" s="12"/>
-      <c r="K133" s="12"/>
       <c r="L133" s="12"/>
-      <c r="N133" s="21"/>
-    </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N133" s="20"/>
+    </row>
+    <row r="134" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A134" s="9">
         <v>39448</v>
       </c>
@@ -4617,14 +4090,10 @@
       <c r="G134" s="2">
         <v>10568</v>
       </c>
-      <c r="H134" s="12"/>
-      <c r="I134" s="12"/>
-      <c r="J134" s="12"/>
-      <c r="K134" s="12"/>
       <c r="L134" s="12"/>
-      <c r="N134" s="21"/>
-    </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N134" s="20"/>
+    </row>
+    <row r="135" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A135" s="9">
         <v>39479</v>
       </c>
@@ -4647,14 +4116,10 @@
       <c r="G135" s="2">
         <v>10645</v>
       </c>
-      <c r="H135" s="12"/>
-      <c r="I135" s="12"/>
-      <c r="J135" s="12"/>
-      <c r="K135" s="12"/>
       <c r="L135" s="12"/>
-      <c r="N135" s="21"/>
-    </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N135" s="20"/>
+    </row>
+    <row r="136" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A136" s="9">
         <v>39508</v>
       </c>
@@ -4677,14 +4142,10 @@
       <c r="G136" s="2">
         <v>10877</v>
       </c>
-      <c r="H136" s="12"/>
-      <c r="I136" s="12"/>
-      <c r="J136" s="12"/>
-      <c r="K136" s="12"/>
       <c r="L136" s="12"/>
-      <c r="N136" s="21"/>
-    </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N136" s="20"/>
+    </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A137" s="9">
         <v>39539</v>
       </c>
@@ -4707,14 +4168,10 @@
       <c r="G137" s="2">
         <v>10753</v>
       </c>
-      <c r="H137" s="12"/>
-      <c r="I137" s="12"/>
-      <c r="J137" s="12"/>
-      <c r="K137" s="12"/>
       <c r="L137" s="12"/>
-      <c r="N137" s="21"/>
-    </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N137" s="20"/>
+    </row>
+    <row r="138" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A138" s="9">
         <v>39569</v>
       </c>
@@ -4737,14 +4194,10 @@
       <c r="G138" s="2">
         <v>10469</v>
       </c>
-      <c r="H138" s="12"/>
-      <c r="I138" s="12"/>
-      <c r="J138" s="12"/>
-      <c r="K138" s="12"/>
       <c r="L138" s="12"/>
-      <c r="N138" s="21"/>
-    </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N138" s="20"/>
+    </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A139" s="9">
         <v>39600</v>
       </c>
@@ -4767,14 +4220,10 @@
       <c r="G139" s="2">
         <v>10292</v>
       </c>
-      <c r="H139" s="12"/>
-      <c r="I139" s="12"/>
-      <c r="J139" s="12"/>
-      <c r="K139" s="12"/>
       <c r="L139" s="12"/>
-      <c r="N139" s="21"/>
-    </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N139" s="20"/>
+    </row>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A140" s="9">
         <v>39630</v>
       </c>
@@ -4797,14 +4246,10 @@
       <c r="G140" s="2">
         <v>10322</v>
       </c>
-      <c r="H140" s="12"/>
-      <c r="I140" s="12"/>
-      <c r="J140" s="12"/>
-      <c r="K140" s="12"/>
       <c r="L140" s="12"/>
-      <c r="N140" s="21"/>
-    </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N140" s="20"/>
+    </row>
+    <row r="141" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A141" s="9">
         <v>39661</v>
       </c>
@@ -4827,14 +4272,10 @@
       <c r="G141" s="2">
         <v>10545</v>
       </c>
-      <c r="H141" s="12"/>
-      <c r="I141" s="12"/>
-      <c r="J141" s="12"/>
-      <c r="K141" s="12"/>
       <c r="L141" s="12"/>
-      <c r="N141" s="21"/>
-    </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N141" s="20"/>
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A142" s="9">
         <v>39692</v>
       </c>
@@ -4857,14 +4298,10 @@
       <c r="G142" s="2">
         <v>10483</v>
       </c>
-      <c r="H142" s="12"/>
-      <c r="I142" s="12"/>
-      <c r="J142" s="12"/>
-      <c r="K142" s="12"/>
       <c r="L142" s="12"/>
-      <c r="N142" s="21"/>
-    </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N142" s="20"/>
+    </row>
+    <row r="143" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A143" s="9">
         <v>39722</v>
       </c>
@@ -4887,14 +4324,10 @@
       <c r="G143" s="2">
         <v>9786</v>
       </c>
-      <c r="H143" s="12"/>
-      <c r="I143" s="12"/>
-      <c r="J143" s="12"/>
-      <c r="K143" s="12"/>
       <c r="L143" s="12"/>
-      <c r="N143" s="21"/>
-    </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N143" s="20"/>
+    </row>
+    <row r="144" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A144" s="9">
         <v>39753</v>
       </c>
@@ -4917,14 +4350,10 @@
       <c r="G144" s="2">
         <v>9263</v>
       </c>
-      <c r="H144" s="12"/>
-      <c r="I144" s="12"/>
-      <c r="J144" s="12"/>
-      <c r="K144" s="12"/>
       <c r="L144" s="12"/>
-      <c r="N144" s="21"/>
-    </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N144" s="20"/>
+    </row>
+    <row r="145" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A145" s="9">
         <v>39783</v>
       </c>
@@ -4947,14 +4376,10 @@
       <c r="G145" s="2">
         <v>9353</v>
       </c>
-      <c r="H145" s="12"/>
-      <c r="I145" s="12"/>
-      <c r="J145" s="12"/>
-      <c r="K145" s="12"/>
       <c r="L145" s="12"/>
-      <c r="N145" s="21"/>
-    </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N145" s="20"/>
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A146" s="9">
         <v>39814</v>
       </c>
@@ -4977,14 +4402,10 @@
       <c r="G146" s="2">
         <v>9862</v>
       </c>
-      <c r="H146" s="12"/>
-      <c r="I146" s="12"/>
-      <c r="J146" s="12"/>
-      <c r="K146" s="12"/>
       <c r="L146" s="12"/>
-      <c r="N146" s="21"/>
-    </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N146" s="20"/>
+    </row>
+    <row r="147" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A147" s="9">
         <v>39845</v>
       </c>
@@ -5007,14 +4428,10 @@
       <c r="G147" s="2">
         <v>10457</v>
       </c>
-      <c r="H147" s="12"/>
-      <c r="I147" s="12"/>
-      <c r="J147" s="12"/>
-      <c r="K147" s="12"/>
       <c r="L147" s="12"/>
-      <c r="N147" s="21"/>
-    </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N147" s="20"/>
+    </row>
+    <row r="148" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A148" s="9">
         <v>39873</v>
       </c>
@@ -5037,14 +4454,10 @@
       <c r="G148" s="2">
         <v>10874</v>
       </c>
-      <c r="H148" s="12"/>
-      <c r="I148" s="12"/>
-      <c r="J148" s="12"/>
-      <c r="K148" s="12"/>
       <c r="L148" s="12"/>
-      <c r="N148" s="21"/>
-    </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N148" s="20"/>
+    </row>
+    <row r="149" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A149" s="9">
         <v>39904</v>
       </c>
@@ -5067,14 +4480,10 @@
       <c r="G149" s="2">
         <v>10934</v>
       </c>
-      <c r="H149" s="12"/>
-      <c r="I149" s="12"/>
-      <c r="J149" s="12"/>
-      <c r="K149" s="12"/>
       <c r="L149" s="12"/>
-      <c r="N149" s="21"/>
-    </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N149" s="20"/>
+    </row>
+    <row r="150" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A150" s="9">
         <v>39934</v>
       </c>
@@ -5097,14 +4506,10 @@
       <c r="G150" s="2">
         <v>11207</v>
       </c>
-      <c r="H150" s="12"/>
-      <c r="I150" s="12"/>
-      <c r="J150" s="12"/>
-      <c r="K150" s="12"/>
       <c r="L150" s="12"/>
-      <c r="N150" s="21"/>
-    </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N150" s="20"/>
+    </row>
+    <row r="151" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A151" s="9">
         <v>39965</v>
       </c>
@@ -5127,14 +4532,10 @@
       <c r="G151" s="2">
         <v>11594</v>
       </c>
-      <c r="H151" s="12"/>
-      <c r="I151" s="12"/>
-      <c r="J151" s="12"/>
-      <c r="K151" s="12"/>
       <c r="L151" s="12"/>
-      <c r="N151" s="21"/>
-    </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N151" s="20"/>
+    </row>
+    <row r="152" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A152" s="9">
         <v>39995</v>
       </c>
@@ -5157,14 +4558,10 @@
       <c r="G152" s="2">
         <v>11719</v>
       </c>
-      <c r="H152" s="12"/>
-      <c r="I152" s="12"/>
-      <c r="J152" s="12"/>
-      <c r="K152" s="12"/>
       <c r="L152" s="12"/>
-      <c r="N152" s="21"/>
-    </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N152" s="20"/>
+    </row>
+    <row r="153" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A153" s="9">
         <v>40026</v>
       </c>
@@ -5187,14 +4584,10 @@
       <c r="G153" s="2">
         <v>11848</v>
       </c>
-      <c r="H153" s="12"/>
-      <c r="I153" s="12"/>
-      <c r="J153" s="12"/>
-      <c r="K153" s="12"/>
       <c r="L153" s="12"/>
-      <c r="N153" s="21"/>
-    </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N153" s="20"/>
+    </row>
+    <row r="154" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A154" s="9">
         <v>40057</v>
       </c>
@@ -5217,14 +4610,10 @@
       <c r="G154" s="2">
         <v>12111</v>
       </c>
-      <c r="H154" s="12"/>
-      <c r="I154" s="12"/>
-      <c r="J154" s="12"/>
-      <c r="K154" s="12"/>
       <c r="L154" s="12"/>
-      <c r="N154" s="21"/>
-    </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N154" s="20"/>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A155" s="9">
         <v>40087</v>
       </c>
@@ -5247,14 +4636,10 @@
       <c r="G155" s="2">
         <v>11785</v>
       </c>
-      <c r="H155" s="12"/>
-      <c r="I155" s="12"/>
-      <c r="J155" s="12"/>
-      <c r="K155" s="12"/>
       <c r="L155" s="12"/>
-      <c r="N155" s="21"/>
-    </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N155" s="20"/>
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A156" s="9">
         <v>40118</v>
       </c>
@@ -5277,14 +4662,10 @@
       <c r="G156" s="2">
         <v>11598</v>
       </c>
-      <c r="H156" s="12"/>
-      <c r="I156" s="12"/>
-      <c r="J156" s="12"/>
-      <c r="K156" s="12"/>
       <c r="L156" s="12"/>
-      <c r="N156" s="21"/>
-    </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N156" s="20"/>
+    </row>
+    <row r="157" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A157" s="9">
         <v>40148</v>
       </c>
@@ -5307,14 +4688,10 @@
       <c r="G157" s="2">
         <v>11662</v>
       </c>
-      <c r="H157" s="12"/>
-      <c r="I157" s="12"/>
-      <c r="J157" s="12"/>
-      <c r="K157" s="12"/>
       <c r="L157" s="12"/>
-      <c r="N157" s="21"/>
-    </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N157" s="20"/>
+    </row>
+    <row r="158" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A158" s="9">
         <v>40179</v>
       </c>
@@ -5337,14 +4714,10 @@
       <c r="G158" s="2">
         <v>11725</v>
       </c>
-      <c r="H158" s="12"/>
-      <c r="I158" s="12"/>
-      <c r="J158" s="12"/>
-      <c r="K158" s="12"/>
       <c r="L158" s="12"/>
-      <c r="N158" s="21"/>
-    </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N158" s="20"/>
+    </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A159" s="9">
         <v>40210</v>
       </c>
@@ -5367,14 +4740,10 @@
       <c r="G159" s="2">
         <v>12072</v>
       </c>
-      <c r="H159" s="12"/>
-      <c r="I159" s="12"/>
-      <c r="J159" s="12"/>
-      <c r="K159" s="12"/>
       <c r="L159" s="12"/>
-      <c r="N159" s="21"/>
-    </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N159" s="20"/>
+    </row>
+    <row r="160" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A160" s="9">
         <v>40238</v>
       </c>
@@ -5397,14 +4766,10 @@
       <c r="G160" s="2">
         <v>12589</v>
       </c>
-      <c r="H160" s="12"/>
-      <c r="I160" s="12"/>
-      <c r="J160" s="12"/>
-      <c r="K160" s="12"/>
       <c r="L160" s="12"/>
-      <c r="N160" s="21"/>
-    </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N160" s="20"/>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A161" s="9">
         <v>40269</v>
       </c>
@@ -5427,14 +4792,10 @@
       <c r="G161" s="2">
         <v>12685</v>
       </c>
-      <c r="H161" s="12"/>
-      <c r="I161" s="12"/>
-      <c r="J161" s="12"/>
-      <c r="K161" s="12"/>
       <c r="L161" s="12"/>
-      <c r="N161" s="21"/>
-    </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N161" s="20"/>
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A162" s="9">
         <v>40299</v>
       </c>
@@ -5457,14 +4818,10 @@
       <c r="G162" s="2">
         <v>12612</v>
       </c>
-      <c r="H162" s="12"/>
-      <c r="I162" s="12"/>
-      <c r="J162" s="12"/>
-      <c r="K162" s="12"/>
       <c r="L162" s="12"/>
-      <c r="N162" s="21"/>
-    </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N162" s="20"/>
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A163" s="9">
         <v>40330</v>
       </c>
@@ -5487,14 +4844,10 @@
       <c r="G163" s="2">
         <v>12483</v>
       </c>
-      <c r="H163" s="12"/>
-      <c r="I163" s="12"/>
-      <c r="J163" s="12"/>
-      <c r="K163" s="12"/>
       <c r="L163" s="12"/>
-      <c r="N163" s="21"/>
-    </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N163" s="20"/>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A164" s="9">
         <v>40360</v>
       </c>
@@ -5517,14 +4870,10 @@
       <c r="G164" s="2">
         <v>12421</v>
       </c>
-      <c r="H164" s="12"/>
-      <c r="I164" s="12"/>
-      <c r="J164" s="12"/>
-      <c r="K164" s="12"/>
       <c r="L164" s="12"/>
-      <c r="N164" s="21"/>
-    </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N164" s="20"/>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A165" s="9">
         <v>40391</v>
       </c>
@@ -5547,14 +4896,10 @@
       <c r="G165" s="2">
         <v>12409</v>
       </c>
-      <c r="H165" s="12"/>
-      <c r="I165" s="12"/>
-      <c r="J165" s="12"/>
-      <c r="K165" s="12"/>
       <c r="L165" s="12"/>
-      <c r="N165" s="21"/>
-    </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N165" s="20"/>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A166" s="9">
         <v>40422</v>
       </c>
@@ -5577,14 +4922,10 @@
       <c r="G166" s="2">
         <v>12353</v>
       </c>
-      <c r="H166" s="12"/>
-      <c r="I166" s="12"/>
-      <c r="J166" s="12"/>
-      <c r="K166" s="12"/>
       <c r="L166" s="12"/>
-      <c r="N166" s="21"/>
-    </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N166" s="20"/>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A167" s="9">
         <v>40452</v>
       </c>
@@ -5607,14 +4948,10 @@
       <c r="G167" s="2">
         <v>12176</v>
       </c>
-      <c r="H167" s="12"/>
-      <c r="I167" s="12"/>
-      <c r="J167" s="12"/>
-      <c r="K167" s="12"/>
       <c r="L167" s="12"/>
-      <c r="N167" s="21"/>
-    </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N167" s="20"/>
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A168" s="9">
         <v>40483</v>
       </c>
@@ -5637,14 +4974,10 @@
       <c r="G168" s="2">
         <v>12183</v>
       </c>
-      <c r="H168" s="12"/>
-      <c r="I168" s="12"/>
-      <c r="J168" s="12"/>
-      <c r="K168" s="12"/>
       <c r="L168" s="12"/>
-      <c r="N168" s="21"/>
-    </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N168" s="20"/>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A169" s="9">
         <v>40513</v>
       </c>
@@ -5667,14 +5000,10 @@
       <c r="G169" s="2">
         <v>12236</v>
       </c>
-      <c r="H169" s="12"/>
-      <c r="I169" s="12"/>
-      <c r="J169" s="12"/>
-      <c r="K169" s="12"/>
       <c r="L169" s="12"/>
-      <c r="N169" s="21"/>
-    </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N169" s="20"/>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A170" s="9">
         <v>40544</v>
       </c>
@@ -5697,15 +5026,11 @@
       <c r="G170" s="2">
         <v>12339</v>
       </c>
-      <c r="H170" s="12"/>
-      <c r="I170" s="12"/>
-      <c r="J170" s="12"/>
-      <c r="K170" s="12"/>
       <c r="L170" s="12"/>
       <c r="N170" s="13"/>
       <c r="O170" s="13"/>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A171" s="9">
         <v>40575</v>
       </c>
@@ -5728,15 +5053,11 @@
       <c r="G171" s="2">
         <v>12510</v>
       </c>
-      <c r="H171" s="12"/>
-      <c r="I171" s="12"/>
-      <c r="J171" s="12"/>
-      <c r="K171" s="12"/>
       <c r="L171" s="12"/>
       <c r="N171" s="13"/>
       <c r="O171" s="13"/>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A172" s="9">
         <v>40603</v>
       </c>
@@ -5759,15 +5080,11 @@
       <c r="G172" s="2">
         <v>12976</v>
       </c>
-      <c r="H172" s="12"/>
-      <c r="I172" s="12"/>
-      <c r="J172" s="12"/>
-      <c r="K172" s="12"/>
       <c r="L172" s="12"/>
       <c r="N172" s="13"/>
       <c r="O172" s="13"/>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A173" s="9">
         <v>40634</v>
       </c>
@@ -5790,15 +5107,11 @@
       <c r="G173" s="2">
         <v>13141</v>
       </c>
-      <c r="H173" s="12"/>
-      <c r="I173" s="12"/>
-      <c r="J173" s="12"/>
-      <c r="K173" s="12"/>
       <c r="L173" s="12"/>
       <c r="N173" s="13"/>
       <c r="O173" s="13"/>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A174" s="9">
         <v>40664</v>
       </c>
@@ -5821,15 +5134,11 @@
       <c r="G174" s="2">
         <v>13007</v>
       </c>
-      <c r="H174" s="12"/>
-      <c r="I174" s="12"/>
-      <c r="J174" s="12"/>
-      <c r="K174" s="12"/>
       <c r="L174" s="12"/>
       <c r="N174" s="13"/>
       <c r="O174" s="13"/>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A175" s="9">
         <v>40695</v>
       </c>
@@ -5852,15 +5161,11 @@
       <c r="G175" s="2">
         <v>12879</v>
       </c>
-      <c r="H175" s="12"/>
-      <c r="I175" s="12"/>
-      <c r="J175" s="12"/>
-      <c r="K175" s="12"/>
       <c r="L175" s="12"/>
       <c r="N175" s="13"/>
       <c r="O175" s="13"/>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A176" s="9">
         <v>40725</v>
       </c>
@@ -5883,15 +5188,11 @@
       <c r="G176" s="2">
         <v>12731</v>
       </c>
-      <c r="H176" s="12"/>
-      <c r="I176" s="12"/>
-      <c r="J176" s="12"/>
-      <c r="K176" s="12"/>
       <c r="L176" s="12"/>
       <c r="N176" s="13"/>
       <c r="O176" s="13"/>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A177" s="9">
         <v>40756</v>
       </c>
@@ -5914,15 +5215,11 @@
       <c r="G177" s="2">
         <v>12602</v>
       </c>
-      <c r="H177" s="12"/>
-      <c r="I177" s="12"/>
-      <c r="J177" s="12"/>
-      <c r="K177" s="12"/>
       <c r="L177" s="12"/>
       <c r="N177" s="13"/>
       <c r="O177" s="13"/>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A178" s="9">
         <v>40787</v>
       </c>
@@ -5945,15 +5242,11 @@
       <c r="G178" s="2">
         <v>12412</v>
       </c>
-      <c r="H178" s="12"/>
-      <c r="I178" s="12"/>
-      <c r="J178" s="12"/>
-      <c r="K178" s="12"/>
       <c r="L178" s="12"/>
       <c r="N178" s="13"/>
       <c r="O178" s="13"/>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A179" s="9">
         <v>40817</v>
       </c>
@@ -5976,15 +5269,11 @@
       <c r="G179" s="2">
         <v>12141</v>
       </c>
-      <c r="H179" s="12"/>
-      <c r="I179" s="12"/>
-      <c r="J179" s="12"/>
-      <c r="K179" s="12"/>
       <c r="L179" s="12"/>
       <c r="N179" s="13"/>
       <c r="O179" s="13"/>
     </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A180" s="9">
         <v>40848</v>
       </c>
@@ -6007,15 +5296,11 @@
       <c r="G180" s="2">
         <v>12107</v>
       </c>
-      <c r="H180" s="12"/>
-      <c r="I180" s="12"/>
-      <c r="J180" s="12"/>
-      <c r="K180" s="12"/>
       <c r="L180" s="12"/>
       <c r="N180" s="13"/>
       <c r="O180" s="13"/>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A181" s="9">
         <v>40878</v>
       </c>
@@ -6038,15 +5323,11 @@
       <c r="G181" s="2">
         <v>12179</v>
       </c>
-      <c r="H181" s="12"/>
-      <c r="I181" s="12"/>
-      <c r="J181" s="12"/>
-      <c r="K181" s="12"/>
       <c r="L181" s="12"/>
       <c r="N181" s="13"/>
       <c r="O181" s="13"/>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A182" s="9">
         <v>40909</v>
       </c>
@@ -6069,15 +5350,11 @@
       <c r="G182" s="2">
         <v>12198</v>
       </c>
-      <c r="H182" s="12"/>
-      <c r="I182" s="12"/>
-      <c r="J182" s="12"/>
-      <c r="K182" s="12"/>
       <c r="L182" s="12"/>
       <c r="N182" s="13"/>
       <c r="O182" s="13"/>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A183" s="9">
         <v>40940</v>
       </c>
@@ -6100,15 +5377,11 @@
       <c r="G183" s="2">
         <v>12377</v>
       </c>
-      <c r="H183" s="12"/>
-      <c r="I183" s="12"/>
-      <c r="J183" s="12"/>
-      <c r="K183" s="12"/>
       <c r="L183" s="12"/>
       <c r="N183" s="13"/>
       <c r="O183" s="13"/>
     </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A184" s="9">
         <v>40969</v>
       </c>
@@ -6131,15 +5404,11 @@
       <c r="G184" s="2">
         <v>12893</v>
       </c>
-      <c r="H184" s="12"/>
-      <c r="I184" s="12"/>
-      <c r="J184" s="12"/>
-      <c r="K184" s="12"/>
       <c r="L184" s="12"/>
       <c r="N184" s="13"/>
       <c r="O184" s="13"/>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A185" s="9">
         <v>41000</v>
       </c>
@@ -6162,15 +5431,11 @@
       <c r="G185" s="2">
         <v>12944</v>
       </c>
-      <c r="H185" s="12"/>
-      <c r="I185" s="12"/>
-      <c r="J185" s="12"/>
-      <c r="K185" s="12"/>
       <c r="L185" s="12"/>
       <c r="N185" s="13"/>
       <c r="O185" s="13"/>
     </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A186" s="9">
         <v>41030</v>
       </c>
@@ -6193,15 +5458,11 @@
       <c r="G186" s="2">
         <v>12647</v>
       </c>
-      <c r="H186" s="12"/>
-      <c r="I186" s="12"/>
-      <c r="J186" s="12"/>
-      <c r="K186" s="12"/>
       <c r="L186" s="12"/>
       <c r="N186" s="13"/>
       <c r="O186" s="13"/>
     </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A187" s="9">
         <v>41061</v>
       </c>
@@ -6224,15 +5485,11 @@
       <c r="G187" s="2">
         <v>12345</v>
       </c>
-      <c r="H187" s="12"/>
-      <c r="I187" s="12"/>
-      <c r="J187" s="12"/>
-      <c r="K187" s="12"/>
       <c r="L187" s="12"/>
       <c r="N187" s="13"/>
       <c r="O187" s="13"/>
     </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A188" s="9">
         <v>41091</v>
       </c>
@@ -6255,15 +5512,11 @@
       <c r="G188" s="2">
         <v>12118</v>
       </c>
-      <c r="H188" s="12"/>
-      <c r="I188" s="12"/>
-      <c r="J188" s="12"/>
-      <c r="K188" s="12"/>
       <c r="L188" s="12"/>
       <c r="N188" s="13"/>
       <c r="O188" s="13"/>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A189" s="9">
         <v>41122</v>
       </c>
@@ -6286,15 +5539,11 @@
       <c r="G189" s="2">
         <v>12036</v>
       </c>
-      <c r="H189" s="12"/>
-      <c r="I189" s="12"/>
-      <c r="J189" s="12"/>
-      <c r="K189" s="12"/>
       <c r="L189" s="12"/>
       <c r="N189" s="13"/>
       <c r="O189" s="13"/>
     </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A190" s="9">
         <v>41153</v>
       </c>
@@ -6317,15 +5566,11 @@
       <c r="G190" s="2">
         <v>11943</v>
       </c>
-      <c r="H190" s="12"/>
-      <c r="I190" s="12"/>
-      <c r="J190" s="12"/>
-      <c r="K190" s="12"/>
       <c r="L190" s="12"/>
       <c r="N190" s="13"/>
       <c r="O190" s="13"/>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A191" s="9">
         <v>41183</v>
       </c>
@@ -6348,15 +5593,11 @@
       <c r="G191" s="2">
         <v>11827</v>
       </c>
-      <c r="H191" s="12"/>
-      <c r="I191" s="12"/>
-      <c r="J191" s="12"/>
-      <c r="K191" s="12"/>
       <c r="L191" s="12"/>
       <c r="N191" s="13"/>
       <c r="O191" s="13"/>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A192" s="9">
         <v>41214</v>
       </c>
@@ -6379,15 +5620,11 @@
       <c r="G192" s="2">
         <v>11804</v>
       </c>
-      <c r="H192" s="12"/>
-      <c r="I192" s="12"/>
-      <c r="J192" s="12"/>
-      <c r="K192" s="12"/>
       <c r="L192" s="12"/>
       <c r="N192" s="13"/>
       <c r="O192" s="13"/>
     </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A193" s="9">
         <v>41244</v>
       </c>
@@ -6410,15 +5647,11 @@
       <c r="G193" s="2">
         <v>11995</v>
       </c>
-      <c r="H193" s="12"/>
-      <c r="I193" s="12"/>
-      <c r="J193" s="12"/>
-      <c r="K193" s="12"/>
       <c r="L193" s="12"/>
       <c r="N193" s="13"/>
       <c r="O193" s="13"/>
     </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A194" s="9">
         <v>41275</v>
       </c>
@@ -6441,15 +5674,11 @@
       <c r="G194" s="2">
         <v>11982</v>
       </c>
-      <c r="H194" s="12"/>
-      <c r="I194" s="12"/>
-      <c r="J194" s="12"/>
-      <c r="K194" s="12"/>
       <c r="L194" s="12"/>
       <c r="N194" s="13"/>
       <c r="O194" s="13"/>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A195" s="9">
         <v>41306</v>
       </c>
@@ -6487,15 +5716,11 @@
       <c r="G195" s="2">
         <v>12035</v>
       </c>
-      <c r="H195" s="12"/>
-      <c r="I195" s="12"/>
-      <c r="J195" s="12"/>
-      <c r="K195" s="12"/>
       <c r="L195" s="12"/>
       <c r="N195" s="13"/>
       <c r="O195" s="13"/>
     </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A196" s="9">
         <v>41334</v>
       </c>
@@ -6518,15 +5743,11 @@
       <c r="G196" s="2">
         <v>12347</v>
       </c>
-      <c r="H196" s="12"/>
-      <c r="I196" s="12"/>
-      <c r="J196" s="12"/>
-      <c r="K196" s="12"/>
       <c r="L196" s="12"/>
       <c r="N196" s="13"/>
       <c r="O196" s="13"/>
     </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A197" s="9">
         <v>41365</v>
       </c>
@@ -6549,15 +5770,11 @@
       <c r="G197" s="2">
         <v>12331</v>
       </c>
-      <c r="H197" s="12"/>
-      <c r="I197" s="12"/>
-      <c r="J197" s="12"/>
-      <c r="K197" s="12"/>
       <c r="L197" s="12"/>
       <c r="N197" s="13"/>
       <c r="O197" s="13"/>
     </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A198" s="9">
         <v>41395</v>
       </c>
@@ -6580,15 +5797,11 @@
       <c r="G198" s="2">
         <v>12188</v>
       </c>
-      <c r="H198" s="12"/>
-      <c r="I198" s="12"/>
-      <c r="J198" s="12"/>
-      <c r="K198" s="12"/>
       <c r="L198" s="12"/>
       <c r="N198" s="13"/>
       <c r="O198" s="13"/>
     </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A199" s="9">
         <v>41426</v>
       </c>
@@ -6611,15 +5824,11 @@
       <c r="G199" s="2">
         <v>12127</v>
       </c>
-      <c r="H199" s="12"/>
-      <c r="I199" s="12"/>
-      <c r="J199" s="12"/>
-      <c r="K199" s="12"/>
       <c r="L199" s="12"/>
       <c r="N199" s="13"/>
       <c r="O199" s="13"/>
     </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A200" s="9">
         <v>41456</v>
       </c>
@@ -6642,15 +5851,11 @@
       <c r="G200" s="2">
         <v>12089</v>
       </c>
-      <c r="H200" s="12"/>
-      <c r="I200" s="12"/>
-      <c r="J200" s="12"/>
-      <c r="K200" s="12"/>
       <c r="L200" s="12"/>
       <c r="N200" s="13"/>
       <c r="O200" s="13"/>
     </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A201" s="9">
         <v>41487</v>
       </c>
@@ -6673,15 +5878,11 @@
       <c r="G201" s="2">
         <v>12139</v>
       </c>
-      <c r="H201" s="12"/>
-      <c r="I201" s="12"/>
-      <c r="J201" s="12"/>
-      <c r="K201" s="12"/>
       <c r="L201" s="12"/>
       <c r="N201" s="13"/>
       <c r="O201" s="13"/>
     </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A202" s="9">
         <v>41518</v>
       </c>
@@ -6704,15 +5905,11 @@
       <c r="G202" s="2">
         <v>11994</v>
       </c>
-      <c r="H202" s="12"/>
-      <c r="I202" s="12"/>
-      <c r="J202" s="12"/>
-      <c r="K202" s="12"/>
       <c r="L202" s="12"/>
       <c r="N202" s="13"/>
       <c r="O202" s="13"/>
     </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A203" s="9">
         <v>41548</v>
       </c>
@@ -6735,15 +5932,11 @@
       <c r="G203" s="2">
         <v>11777</v>
       </c>
-      <c r="H203" s="12"/>
-      <c r="I203" s="12"/>
-      <c r="J203" s="12"/>
-      <c r="K203" s="12"/>
       <c r="L203" s="12"/>
       <c r="N203" s="13"/>
       <c r="O203" s="13"/>
     </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A204" s="9">
         <v>41579</v>
       </c>
@@ -6766,15 +5959,11 @@
       <c r="G204" s="2">
         <v>11803</v>
       </c>
-      <c r="H204" s="12"/>
-      <c r="I204" s="12"/>
-      <c r="J204" s="12"/>
-      <c r="K204" s="12"/>
       <c r="L204" s="12"/>
       <c r="N204" s="13"/>
       <c r="O204" s="13"/>
     </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A205" s="9">
         <v>41609</v>
       </c>
@@ -6797,15 +5986,11 @@
       <c r="G205" s="2">
         <v>11884</v>
       </c>
-      <c r="H205" s="12"/>
-      <c r="I205" s="12"/>
-      <c r="J205" s="12"/>
-      <c r="K205" s="12"/>
       <c r="L205" s="12"/>
       <c r="N205" s="13"/>
       <c r="O205" s="13"/>
     </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A206" s="9">
         <v>41640</v>
       </c>
@@ -6828,15 +6013,11 @@
       <c r="G206" s="2">
         <v>11984</v>
       </c>
-      <c r="H206" s="12"/>
-      <c r="I206" s="12"/>
-      <c r="J206" s="12"/>
-      <c r="K206" s="12"/>
       <c r="L206" s="12"/>
       <c r="N206" s="13"/>
       <c r="O206" s="13"/>
     </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A207" s="9">
         <v>41671</v>
       </c>
@@ -6859,15 +6040,11 @@
       <c r="G207" s="2">
         <v>12254</v>
       </c>
-      <c r="H207" s="12"/>
-      <c r="I207" s="12"/>
-      <c r="J207" s="12"/>
-      <c r="K207" s="12"/>
       <c r="L207" s="12"/>
       <c r="N207" s="13"/>
       <c r="O207" s="13"/>
     </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A208" s="9">
         <v>41699</v>
       </c>
@@ -6890,15 +6067,11 @@
       <c r="G208" s="2">
         <v>12803</v>
       </c>
-      <c r="H208" s="12"/>
-      <c r="I208" s="12"/>
-      <c r="J208" s="12"/>
-      <c r="K208" s="12"/>
       <c r="L208" s="12"/>
       <c r="N208" s="13"/>
       <c r="O208" s="13"/>
     </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A209" s="9">
         <v>41730</v>
       </c>
@@ -6921,15 +6094,11 @@
       <c r="G209" s="2">
         <v>12892</v>
       </c>
-      <c r="H209" s="12"/>
-      <c r="I209" s="12"/>
-      <c r="J209" s="12"/>
-      <c r="K209" s="12"/>
       <c r="L209" s="12"/>
       <c r="N209" s="13"/>
       <c r="O209" s="13"/>
     </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A210" s="9">
         <v>41760</v>
       </c>
@@ -6952,15 +6121,11 @@
       <c r="G210" s="2">
         <v>12680</v>
       </c>
-      <c r="H210" s="12"/>
-      <c r="I210" s="12"/>
-      <c r="J210" s="12"/>
-      <c r="K210" s="12"/>
       <c r="L210" s="12"/>
       <c r="N210" s="13"/>
       <c r="O210" s="13"/>
     </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A211" s="9">
         <v>41791</v>
       </c>
@@ -6983,15 +6148,11 @@
       <c r="G211" s="2">
         <v>12465</v>
       </c>
-      <c r="H211" s="12"/>
-      <c r="I211" s="12"/>
-      <c r="J211" s="12"/>
-      <c r="K211" s="12"/>
       <c r="L211" s="12"/>
       <c r="N211" s="13"/>
       <c r="O211" s="13"/>
     </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A212" s="9">
         <v>41821</v>
       </c>
@@ -7014,15 +6175,11 @@
       <c r="G212" s="2">
         <v>12210</v>
       </c>
-      <c r="H212" s="12"/>
-      <c r="I212" s="12"/>
-      <c r="J212" s="12"/>
-      <c r="K212" s="12"/>
       <c r="L212" s="12"/>
       <c r="N212" s="13"/>
       <c r="O212" s="13"/>
     </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A213" s="9">
         <v>41852</v>
       </c>
@@ -7045,15 +6202,11 @@
       <c r="G213" s="2">
         <v>12112</v>
       </c>
-      <c r="H213" s="12"/>
-      <c r="I213" s="12"/>
-      <c r="J213" s="12"/>
-      <c r="K213" s="12"/>
       <c r="L213" s="12"/>
       <c r="N213" s="13"/>
       <c r="O213" s="13"/>
     </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A214" s="9">
         <v>41883</v>
       </c>
@@ -7076,15 +6229,11 @@
       <c r="G214" s="2">
         <v>11959</v>
       </c>
-      <c r="H214" s="12"/>
-      <c r="I214" s="12"/>
-      <c r="J214" s="12"/>
-      <c r="K214" s="12"/>
       <c r="L214" s="12"/>
       <c r="N214" s="13"/>
       <c r="O214" s="13"/>
     </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A215" s="9">
         <v>41913</v>
       </c>
@@ -7107,15 +6256,11 @@
       <c r="G215" s="2">
         <v>11818</v>
       </c>
-      <c r="H215" s="12"/>
-      <c r="I215" s="12"/>
-      <c r="J215" s="12"/>
-      <c r="K215" s="12"/>
       <c r="L215" s="12"/>
       <c r="N215" s="13"/>
       <c r="O215" s="13"/>
     </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A216" s="9">
         <v>41944</v>
       </c>
@@ -7138,15 +6283,11 @@
       <c r="G216" s="2">
         <v>11978</v>
       </c>
-      <c r="H216" s="12"/>
-      <c r="I216" s="12"/>
-      <c r="J216" s="12"/>
-      <c r="K216" s="12"/>
       <c r="L216" s="12"/>
       <c r="N216" s="13"/>
       <c r="O216" s="13"/>
     </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A217" s="9">
         <v>41974</v>
       </c>
@@ -7169,15 +6310,11 @@
       <c r="G217" s="2">
         <v>12092</v>
       </c>
-      <c r="H217" s="12"/>
-      <c r="I217" s="12"/>
-      <c r="J217" s="12"/>
-      <c r="K217" s="12"/>
       <c r="L217" s="12"/>
       <c r="N217" s="13"/>
       <c r="O217" s="13"/>
     </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A218" s="9">
         <v>42005</v>
       </c>
@@ -7216,7 +6353,7 @@
       <c r="N218" s="13"/>
       <c r="O218" s="13"/>
     </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A219" s="9">
         <v>42036</v>
       </c>
@@ -7255,7 +6392,7 @@
       <c r="N219" s="13"/>
       <c r="O219" s="13"/>
     </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A220" s="9">
         <v>42064</v>
       </c>
@@ -7294,7 +6431,7 @@
       <c r="N220" s="13"/>
       <c r="O220" s="13"/>
     </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A221" s="9">
         <v>42095</v>
       </c>
@@ -7333,7 +6470,7 @@
       <c r="N221" s="13"/>
       <c r="O221" s="13"/>
     </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A222" s="9">
         <v>42125</v>
       </c>
@@ -7372,7 +6509,7 @@
       <c r="N222" s="13"/>
       <c r="O222" s="13"/>
     </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A223" s="9">
         <v>42156</v>
       </c>
@@ -7411,7 +6548,7 @@
       <c r="N223" s="13"/>
       <c r="O223" s="13"/>
     </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A224" s="9">
         <v>42186</v>
       </c>
@@ -7450,7 +6587,7 @@
       <c r="N224" s="13"/>
       <c r="O224" s="13"/>
     </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A225" s="9">
         <v>42217</v>
       </c>
@@ -7489,7 +6626,7 @@
       <c r="N225" s="13"/>
       <c r="O225" s="13"/>
     </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A226" s="9">
         <v>42248</v>
       </c>
@@ -7528,7 +6665,7 @@
       <c r="N226" s="13"/>
       <c r="O226" s="13"/>
     </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A227" s="9">
         <v>42278</v>
       </c>
@@ -7567,7 +6704,7 @@
       <c r="N227" s="13"/>
       <c r="O227" s="13"/>
     </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A228" s="9">
         <v>42309</v>
       </c>
@@ -7606,7 +6743,7 @@
       <c r="N228" s="13"/>
       <c r="O228" s="13"/>
     </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A229" s="9">
         <v>42339</v>
       </c>
@@ -7645,7 +6782,7 @@
       <c r="N229" s="13"/>
       <c r="O229" s="13"/>
     </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A230" s="9">
         <v>42370</v>
       </c>
@@ -7684,7 +6821,7 @@
       <c r="N230" s="13"/>
       <c r="O230" s="13"/>
     </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A231" s="9">
         <v>42401</v>
       </c>
@@ -7723,7 +6860,7 @@
       <c r="N231" s="13"/>
       <c r="O231" s="13"/>
     </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A232" s="9">
         <v>42430</v>
       </c>
@@ -7762,7 +6899,7 @@
       <c r="N232" s="13"/>
       <c r="O232" s="13"/>
     </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A233" s="9">
         <v>42461</v>
       </c>
@@ -7801,7 +6938,7 @@
       <c r="N233" s="13"/>
       <c r="O233" s="13"/>
     </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A234" s="9">
         <v>42491</v>
       </c>
@@ -7840,7 +6977,7 @@
       <c r="N234" s="13"/>
       <c r="O234" s="13"/>
     </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A235" s="9">
         <v>42522</v>
       </c>
@@ -7879,7 +7016,7 @@
       <c r="N235" s="13"/>
       <c r="O235" s="13"/>
     </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A236" s="9">
         <v>42552</v>
       </c>
@@ -7918,7 +7055,7 @@
       <c r="N236" s="13"/>
       <c r="O236" s="13"/>
     </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A237" s="9">
         <v>42583</v>
       </c>
@@ -7957,7 +7094,7 @@
       <c r="N237" s="13"/>
       <c r="O237" s="13"/>
     </row>
-    <row r="238" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A238" s="9">
         <v>42614</v>
       </c>
@@ -7996,7 +7133,7 @@
       <c r="N238" s="13"/>
       <c r="O238" s="13"/>
     </row>
-    <row r="239" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A239" s="9">
         <v>42644</v>
       </c>
@@ -8035,7 +7172,7 @@
       <c r="N239" s="13"/>
       <c r="O239" s="13"/>
     </row>
-    <row r="240" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A240" s="9">
         <v>42675</v>
       </c>
@@ -8074,7 +7211,7 @@
       <c r="N240" s="13"/>
       <c r="O240" s="13"/>
     </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A241" s="9">
         <v>42705</v>
       </c>
@@ -8113,7 +7250,7 @@
       <c r="N241" s="13"/>
       <c r="O241" s="13"/>
     </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A242" s="9">
         <v>42736</v>
       </c>
@@ -8152,7 +7289,7 @@
       <c r="N242" s="13"/>
       <c r="O242" s="13"/>
     </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A243" s="9">
         <v>42767</v>
       </c>
@@ -8191,7 +7328,7 @@
       <c r="N243" s="13"/>
       <c r="O243" s="13"/>
     </row>
-    <row r="244" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A244" s="9">
         <v>42795</v>
       </c>
@@ -8227,9 +7364,9 @@
         <v>100.41850915982313</v>
       </c>
       <c r="L244" s="12"/>
-      <c r="N244" s="21"/>
-    </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N244" s="20"/>
+    </row>
+    <row r="245" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A245" s="9">
         <v>42826</v>
       </c>
@@ -8265,9 +7402,9 @@
         <v>100.63960833859761</v>
       </c>
       <c r="L245" s="12"/>
-      <c r="N245" s="21"/>
-    </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N245" s="20"/>
+    </row>
+    <row r="246" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A246" s="9">
         <v>42856</v>
       </c>
@@ -8303,9 +7440,9 @@
         <v>101.75300063171196</v>
       </c>
       <c r="L246" s="12"/>
-      <c r="N246" s="21"/>
-    </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N246" s="20"/>
+    </row>
+    <row r="247" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A247" s="9">
         <v>42887</v>
       </c>
@@ -8341,9 +7478,9 @@
         <v>102.10044219835757</v>
       </c>
       <c r="L247" s="12"/>
-      <c r="N247" s="21"/>
-    </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N247" s="20"/>
+    </row>
+    <row r="248" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A248" s="9">
         <v>42917</v>
       </c>
@@ -8379,9 +7516,9 @@
         <v>102.31364497789011</v>
       </c>
       <c r="L248" s="12"/>
-      <c r="N248" s="21"/>
-    </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N248" s="20"/>
+    </row>
+    <row r="249" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A249" s="9">
         <v>42948</v>
       </c>
@@ -8417,9 +7554,9 @@
         <v>101.71351863550224</v>
       </c>
       <c r="L249" s="12"/>
-      <c r="N249" s="21"/>
-    </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N249" s="20"/>
+    </row>
+    <row r="250" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A250" s="9">
         <v>42979</v>
       </c>
@@ -8455,9 +7592,9 @@
         <v>103.75868603916616</v>
       </c>
       <c r="L250" s="12"/>
-      <c r="N250" s="21"/>
-    </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N250" s="20"/>
+    </row>
+    <row r="251" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A251" s="9">
         <v>43009</v>
       </c>
@@ -8493,9 +7630,9 @@
         <v>105.69330385344286</v>
       </c>
       <c r="L251" s="12"/>
-      <c r="N251" s="21"/>
-    </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N251" s="20"/>
+    </row>
+    <row r="252" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A252" s="9">
         <v>43040</v>
       </c>
@@ -8531,9 +7668,9 @@
         <v>104.99842072015163</v>
       </c>
       <c r="L252" s="12"/>
-      <c r="N252" s="21"/>
-    </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N252" s="20"/>
+    </row>
+    <row r="253" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A253" s="9">
         <v>43070</v>
       </c>
@@ -8569,9 +7706,9 @@
         <v>104.42198357548959</v>
       </c>
       <c r="L253" s="12"/>
-      <c r="N253" s="21"/>
-    </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N253" s="20"/>
+    </row>
+    <row r="254" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A254" s="9">
         <v>43101</v>
       </c>
@@ -8607,9 +7744,9 @@
         <v>104.80101073910299</v>
       </c>
       <c r="L254" s="12"/>
-      <c r="N254" s="21"/>
-    </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N254" s="20"/>
+    </row>
+    <row r="255" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A255" s="9">
         <v>43132</v>
       </c>
@@ -8645,9 +7782,9 @@
         <v>105.30638029058751</v>
       </c>
       <c r="L255" s="12"/>
-      <c r="N255" s="21"/>
-    </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N255" s="20"/>
+    </row>
+    <row r="256" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A256" s="9">
         <v>43160</v>
       </c>
@@ -8683,9 +7820,9 @@
         <v>105.86702463676566</v>
       </c>
       <c r="L256" s="12"/>
-      <c r="N256" s="21"/>
-    </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N256" s="20"/>
+    </row>
+    <row r="257" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A257" s="9">
         <v>43191</v>
       </c>
@@ -8721,9 +7858,9 @@
         <v>106.38029058749214</v>
       </c>
       <c r="L257" s="12"/>
-      <c r="N257" s="21"/>
-    </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N257" s="20"/>
+    </row>
+    <row r="258" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A258" s="9">
         <v>43221</v>
       </c>
@@ -8759,9 +7896,9 @@
         <v>106.48294377763743</v>
       </c>
       <c r="L258" s="12"/>
-      <c r="N258" s="21"/>
-    </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N258" s="20"/>
+    </row>
+    <row r="259" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A259" s="9">
         <v>43252</v>
       </c>
@@ -8812,9 +7949,9 @@
         <v>106.43556538218576</v>
       </c>
       <c r="L259" s="12"/>
-      <c r="N259" s="21"/>
-    </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N259" s="20"/>
+    </row>
+    <row r="260" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A260" s="9">
         <v>43282</v>
       </c>
@@ -8850,9 +7987,9 @@
         <v>107.48578648136453</v>
       </c>
       <c r="L260" s="12"/>
-      <c r="N260" s="21"/>
-    </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N260" s="20"/>
+    </row>
+    <row r="261" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A261" s="9">
         <v>43313</v>
       </c>
@@ -8888,9 +8025,9 @@
         <v>107.99905243209099</v>
       </c>
       <c r="L261" s="12"/>
-      <c r="N261" s="21"/>
-    </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N261" s="20"/>
+    </row>
+    <row r="262" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A262" s="9">
         <v>43344</v>
       </c>
@@ -8926,9 +8063,9 @@
         <v>108.25173720783324</v>
       </c>
       <c r="L262" s="12"/>
-      <c r="N262" s="21"/>
-    </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N262" s="20"/>
+    </row>
+    <row r="263" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A263" s="9">
         <v>43374</v>
       </c>
@@ -8964,9 +8101,9 @@
         <v>109.08085912823753</v>
       </c>
       <c r="L263" s="12"/>
-      <c r="N263" s="21"/>
-    </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N263" s="20"/>
+    </row>
+    <row r="264" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A264" s="9">
         <v>43405</v>
       </c>
@@ -9002,9 +8139,9 @@
         <v>108.71762476310803</v>
       </c>
       <c r="L264" s="12"/>
-      <c r="N264" s="21"/>
-    </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N264" s="20"/>
+    </row>
+    <row r="265" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A265" s="9">
         <v>43435</v>
       </c>
@@ -9040,9 +8177,9 @@
         <v>108.55180037902717</v>
       </c>
       <c r="L265" s="12"/>
-      <c r="N265" s="21"/>
-    </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N265" s="20"/>
+    </row>
+    <row r="266" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A266" s="9">
         <v>43466</v>
       </c>
@@ -9078,9 +8215,9 @@
         <v>108.03853442830071</v>
       </c>
       <c r="L266" s="12"/>
-      <c r="N266" s="21"/>
-    </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N266" s="20"/>
+    </row>
+    <row r="267" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A267" s="9">
         <v>43497</v>
       </c>
@@ -9116,9 +8253,9 @@
         <v>108.15698041692988</v>
       </c>
       <c r="L267" s="12"/>
-      <c r="N267" s="21"/>
-    </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N267" s="20"/>
+    </row>
+    <row r="268" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A268" s="9">
         <v>43525</v>
       </c>
@@ -9154,9 +8291,9 @@
         <v>108.91503474415667</v>
       </c>
       <c r="L268" s="12"/>
-      <c r="N268" s="21"/>
-    </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N268" s="20"/>
+    </row>
+    <row r="269" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A269" s="9">
         <v>43556</v>
       </c>
@@ -9192,9 +8329,9 @@
         <v>109.60991787744788</v>
       </c>
       <c r="L269" s="12"/>
-      <c r="N269" s="21"/>
-    </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N269" s="20"/>
+    </row>
+    <row r="270" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A270" s="9">
         <v>43586</v>
       </c>
@@ -9230,9 +8367,9 @@
         <v>110.0442198357549</v>
       </c>
       <c r="L270" s="12"/>
-      <c r="N270" s="21"/>
-    </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N270" s="20"/>
+    </row>
+    <row r="271" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A271" s="9">
         <v>43617</v>
       </c>
@@ -9268,9 +8405,9 @@
         <v>110.18635502210992</v>
       </c>
       <c r="L271" s="12"/>
-      <c r="N271" s="21"/>
-    </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N271" s="20"/>
+    </row>
+    <row r="272" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A272" s="9">
         <v>43647</v>
       </c>
@@ -9306,9 +8443,9 @@
         <v>110.73910296904613</v>
       </c>
       <c r="L272" s="12"/>
-      <c r="N272" s="21"/>
-    </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N272" s="20"/>
+    </row>
+    <row r="273" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A273" s="9">
         <v>43678</v>
       </c>
@@ -9344,9 +8481,9 @@
         <v>109.7678458622868</v>
       </c>
       <c r="L273" s="12"/>
-      <c r="N273" s="21"/>
-    </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N273" s="20"/>
+    </row>
+    <row r="274" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A274" s="9">
         <v>43709</v>
       </c>
@@ -9382,9 +8519,9 @@
         <v>109.32564750473786</v>
       </c>
       <c r="L274" s="12"/>
-      <c r="N274" s="21"/>
-    </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N274" s="20"/>
+    </row>
+    <row r="275" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A275" s="9">
         <v>43739</v>
       </c>
@@ -9420,9 +8557,9 @@
         <v>108.46493998736578</v>
       </c>
       <c r="L275" s="12"/>
-      <c r="N275" s="21"/>
-    </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N275" s="20"/>
+    </row>
+    <row r="276" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A276" s="9">
         <v>43770</v>
       </c>
@@ -9458,9 +8595,9 @@
         <v>109.30195830701201</v>
       </c>
       <c r="L276" s="12"/>
-      <c r="N276" s="21"/>
-    </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N276" s="20"/>
+    </row>
+    <row r="277" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A277" s="9">
         <v>43800</v>
       </c>
@@ -9496,9 +8633,9 @@
         <v>111.43398610233734</v>
       </c>
       <c r="L277" s="12"/>
-      <c r="N277" s="21"/>
-    </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N277" s="20"/>
+    </row>
+    <row r="278" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A278" s="9">
         <v>43831</v>
       </c>
@@ -9534,9 +8671,9 @@
         <v>112.83164876816173</v>
       </c>
       <c r="L278" s="12"/>
-      <c r="N278" s="21"/>
-    </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N278" s="20"/>
+    </row>
+    <row r="279" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A279" s="9">
         <v>43862</v>
       </c>
@@ -9572,9 +8709,9 @@
         <v>114.90840176879344</v>
       </c>
       <c r="L279" s="12"/>
-      <c r="N279" s="21"/>
-    </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N279" s="20"/>
+    </row>
+    <row r="280" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A280" s="9">
         <v>43891</v>
       </c>
@@ -9610,9 +8747,9 @@
         <v>112.52368919772584</v>
       </c>
       <c r="L280" s="12"/>
-      <c r="N280" s="21"/>
-    </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N280" s="20"/>
+    </row>
+    <row r="281" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A281" s="9">
         <v>43922</v>
       </c>
@@ -9648,9 +8785,9 @@
         <v>98.42072015161088</v>
       </c>
       <c r="L281" s="12"/>
-      <c r="N281" s="21"/>
-    </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N281" s="20"/>
+    </row>
+    <row r="282" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A282" s="9">
         <v>43952</v>
       </c>
@@ -9686,9 +8823,9 @@
         <v>107.81743524952623</v>
       </c>
       <c r="L282" s="12"/>
-      <c r="N282" s="21"/>
-    </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N282" s="20"/>
+    </row>
+    <row r="283" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A283" s="9">
         <v>43983</v>
       </c>
@@ -9724,9 +8861,9 @@
         <v>117.03253316487684</v>
       </c>
       <c r="L283" s="12"/>
-      <c r="N283" s="21"/>
-    </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N283" s="20"/>
+    </row>
+    <row r="284" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A284" s="9">
         <v>44013</v>
       </c>
@@ -9762,9 +8899,9 @@
         <v>125.86070751737211</v>
       </c>
       <c r="L284" s="12"/>
-      <c r="N284" s="21"/>
-    </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N284" s="20"/>
+    </row>
+    <row r="285" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A285" s="9">
         <v>44044</v>
       </c>
@@ -9800,9 +8937,9 @@
         <v>129.19298799747318</v>
       </c>
       <c r="L285" s="12"/>
-      <c r="N285" s="21"/>
-    </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N285" s="20"/>
+    </row>
+    <row r="286" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A286" s="9">
         <v>44075</v>
       </c>
@@ -9838,9 +8975,9 @@
         <v>127.07675300063175</v>
       </c>
       <c r="L286" s="12"/>
-      <c r="N286" s="21"/>
-    </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N286" s="20"/>
+    </row>
+    <row r="287" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A287" s="9">
         <v>44105</v>
       </c>
@@ -9876,9 +9013,9 @@
         <v>126.61086544535695</v>
       </c>
       <c r="L287" s="12"/>
-      <c r="N287" s="21"/>
-    </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N287" s="20"/>
+    </row>
+    <row r="288" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A288" s="9">
         <v>44136</v>
       </c>
@@ -9914,9 +9051,9 @@
         <v>126.76089703095391</v>
       </c>
       <c r="L288" s="12"/>
-      <c r="N288" s="21"/>
-    </row>
-    <row r="289" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N288" s="20"/>
+    </row>
+    <row r="289" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A289" s="9">
         <v>44166</v>
       </c>
@@ -9952,9 +9089,9 @@
         <v>127.86639292482631</v>
       </c>
       <c r="L289" s="12"/>
-      <c r="N289" s="21"/>
-    </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N289" s="20"/>
+    </row>
+    <row r="290" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A290" s="9">
         <v>44197</v>
       </c>
@@ -9990,9 +9127,9 @@
         <v>130.10107391029695</v>
       </c>
       <c r="L290" s="12"/>
-      <c r="N290" s="21"/>
-    </row>
-    <row r="291" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N290" s="20"/>
+    </row>
+    <row r="291" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A291" s="9">
         <v>44228</v>
       </c>
@@ -10028,9 +9165,9 @@
         <v>135.24162981680357</v>
       </c>
       <c r="L291" s="12"/>
-      <c r="N291" s="21"/>
-    </row>
-    <row r="292" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N291" s="20"/>
+    </row>
+    <row r="292" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A292" s="9">
         <v>44256</v>
       </c>
@@ -10066,9 +9203,9 @@
         <v>142.16677195198994</v>
       </c>
       <c r="L292" s="12"/>
-      <c r="N292" s="21"/>
-    </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N292" s="20"/>
+    </row>
+    <row r="293" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A293" s="9">
         <v>44287</v>
       </c>
@@ -10104,9 +9241,9 @@
         <v>150.0947567909034</v>
       </c>
       <c r="L293" s="12"/>
-      <c r="N293" s="21"/>
-    </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N293" s="20"/>
+    </row>
+    <row r="294" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A294" s="9">
         <v>44317</v>
       </c>
@@ -10142,9 +9279,9 @@
         <v>156.40397978521801</v>
       </c>
       <c r="L294" s="12"/>
-      <c r="N294" s="21"/>
-    </row>
-    <row r="295" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N294" s="20"/>
+    </row>
+    <row r="295" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A295" s="9">
         <v>44348</v>
       </c>
@@ -10180,9 +9317,9 @@
         <v>156.00915982312074</v>
       </c>
       <c r="L295" s="12"/>
-      <c r="N295" s="21"/>
-    </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N295" s="20"/>
+    </row>
+    <row r="296" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A296" s="9">
         <v>44378</v>
       </c>
@@ -10218,9 +9355,9 @@
         <v>155.53537586860401</v>
       </c>
       <c r="L296" s="12"/>
-      <c r="N296" s="21"/>
-    </row>
-    <row r="297" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N296" s="20"/>
+    </row>
+    <row r="297" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A297" s="9">
         <v>44409</v>
       </c>
@@ -10256,9 +9393,9 @@
         <v>155.23531269741008</v>
       </c>
       <c r="L297" s="12"/>
-      <c r="N297" s="21"/>
-    </row>
-    <row r="298" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N297" s="20"/>
+    </row>
+    <row r="298" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A298" s="9">
         <v>44440</v>
       </c>
@@ -10294,9 +9431,9 @@
         <v>165.50063171193946</v>
       </c>
       <c r="L298" s="12"/>
-      <c r="N298" s="21"/>
-    </row>
-    <row r="299" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N298" s="20"/>
+    </row>
+    <row r="299" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A299" s="9">
         <v>44470</v>
       </c>
@@ -10332,9 +9469,9 @@
         <v>175.42640555906516</v>
       </c>
       <c r="L299" s="12"/>
-      <c r="N299" s="21"/>
-    </row>
-    <row r="300" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N299" s="20"/>
+    </row>
+    <row r="300" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A300" s="9">
         <v>44501</v>
       </c>
@@ -10370,9 +9507,9 @@
         <v>180.66961465571708</v>
       </c>
       <c r="L300" s="12"/>
-      <c r="N300" s="21"/>
-    </row>
-    <row r="301" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N300" s="20"/>
+    </row>
+    <row r="301" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A301" s="9">
         <v>44531</v>
       </c>
@@ -10408,9 +9545,9 @@
         <v>182.05148452305758</v>
       </c>
       <c r="L301" s="12"/>
-      <c r="N301" s="21"/>
-    </row>
-    <row r="302" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N301" s="20"/>
+    </row>
+    <row r="302" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A302" s="9">
         <v>44562</v>
       </c>
@@ -10446,9 +9583,9 @@
         <v>181.56980416929889</v>
       </c>
       <c r="L302" s="12"/>
-      <c r="N302" s="21"/>
-    </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N302" s="20"/>
+    </row>
+    <row r="303" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A303" s="9">
         <v>44593</v>
       </c>
@@ -10484,9 +9621,9 @@
         <v>177.08464939987374</v>
       </c>
       <c r="L303" s="12"/>
-      <c r="N303" s="21"/>
-    </row>
-    <row r="304" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N303" s="20"/>
+    </row>
+    <row r="304" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A304" s="9">
         <v>44621</v>
       </c>
@@ -10522,9 +9659,9 @@
         <v>173.63392293114347</v>
       </c>
       <c r="L304" s="12"/>
-      <c r="N304" s="21"/>
-    </row>
-    <row r="305" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N304" s="20"/>
+    </row>
+    <row r="305" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A305" s="9">
         <v>44652</v>
       </c>
@@ -10560,9 +9697,9 @@
         <v>173.22331017056231</v>
       </c>
       <c r="L305" s="12"/>
-      <c r="N305" s="21"/>
-    </row>
-    <row r="306" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N305" s="20"/>
+    </row>
+    <row r="306" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A306" s="9">
         <v>44682</v>
       </c>
@@ -10598,9 +9735,9 @@
         <v>173.26279216677204</v>
       </c>
       <c r="L306" s="12"/>
-      <c r="N306" s="21"/>
-    </row>
-    <row r="307" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N306" s="20"/>
+    </row>
+    <row r="307" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A307" s="9">
         <v>44713</v>
       </c>
@@ -10636,9 +9773,9 @@
         <v>171.19393556538228</v>
       </c>
       <c r="L307" s="12"/>
-      <c r="N307" s="21"/>
-    </row>
-    <row r="308" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N307" s="20"/>
+    </row>
+    <row r="308" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A308" s="9">
         <v>44743</v>
       </c>
@@ -10674,9 +9811,9 @@
         <v>170.23847125710685</v>
       </c>
       <c r="L308" s="12"/>
-      <c r="N308" s="21"/>
-    </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N308" s="20"/>
+    </row>
+    <row r="309" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A309" s="9">
         <v>44774</v>
       </c>
@@ -10712,9 +9849,9 @@
         <v>163.88186986734058</v>
       </c>
       <c r="L309" s="12"/>
-      <c r="N309" s="21"/>
-    </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N309" s="20"/>
+    </row>
+    <row r="310" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A310" s="9">
         <v>44805</v>
       </c>
@@ -10750,9 +9887,9 @@
         <v>161.73404927353135</v>
       </c>
       <c r="L310" s="12"/>
-      <c r="N310" s="21"/>
-    </row>
-    <row r="311" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N310" s="20"/>
+    </row>
+    <row r="311" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A311" s="9">
         <v>44835</v>
       </c>
@@ -10788,9 +9925,9 @@
         <v>158.38597599494639</v>
       </c>
       <c r="L311" s="12"/>
-      <c r="N311" s="21"/>
-    </row>
-    <row r="312" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N311" s="20"/>
+    </row>
+    <row r="312" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A312" s="9">
         <v>44866</v>
       </c>
@@ -10826,9 +9963,9 @@
         <v>157.56475047378404</v>
       </c>
       <c r="L312" s="12"/>
-      <c r="N312" s="21"/>
-    </row>
-    <row r="313" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N312" s="20"/>
+    </row>
+    <row r="313" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A313" s="9">
         <v>44896</v>
       </c>
@@ -10864,9 +10001,9 @@
         <v>158.23594440934943</v>
       </c>
       <c r="L313" s="12"/>
-      <c r="N313" s="21"/>
-    </row>
-    <row r="314" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N313" s="20"/>
+    </row>
+    <row r="314" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A314" s="9">
         <v>44927</v>
       </c>
@@ -10902,9 +10039,9 @@
         <v>161.33133291219212</v>
       </c>
       <c r="L314" s="12"/>
-      <c r="N314" s="21"/>
-    </row>
-    <row r="315" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N314" s="20"/>
+    </row>
+    <row r="315" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A315" s="9">
         <v>44958</v>
       </c>
@@ -10940,9 +10077,9 @@
         <v>166.81933038534439</v>
       </c>
       <c r="L315" s="12"/>
-      <c r="N315" s="21"/>
-    </row>
-    <row r="316" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N315" s="20"/>
+    </row>
+    <row r="316" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A316" s="9">
         <v>44986</v>
       </c>
@@ -10978,9 +10115,9 @@
         <v>168.38281743524962</v>
       </c>
       <c r="L316" s="12"/>
-      <c r="N316" s="21"/>
-    </row>
-    <row r="317" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N316" s="20"/>
+    </row>
+    <row r="317" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A317" s="9">
         <v>45017</v>
       </c>
@@ -11016,9 +10153,9 @@
         <v>163.8344914718889</v>
       </c>
       <c r="L317" s="12"/>
-      <c r="N317" s="21"/>
-    </row>
-    <row r="318" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N317" s="20"/>
+    </row>
+    <row r="318" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A318" s="9">
         <v>45047</v>
       </c>
@@ -11054,9 +10191,9 @@
         <v>159.60202147820601</v>
       </c>
       <c r="L318" s="12"/>
-      <c r="N318" s="21"/>
-    </row>
-    <row r="319" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N318" s="20"/>
+    </row>
+    <row r="319" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A319" s="9">
         <v>45078</v>
       </c>
@@ -11092,9 +10229,9 @@
         <v>155.4327226784587</v>
       </c>
       <c r="L319" s="12"/>
-      <c r="N319" s="21"/>
-    </row>
-    <row r="320" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N319" s="20"/>
+    </row>
+    <row r="320" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A320" s="9">
         <v>45108</v>
       </c>
@@ -11130,9 +10267,9 @@
         <v>152.80322173089081</v>
       </c>
       <c r="L320" s="12"/>
-      <c r="N320" s="21"/>
-    </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N320" s="20"/>
+    </row>
+    <row r="321" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A321" s="9">
         <v>45139</v>
       </c>
@@ -11168,9 +10305,9 @@
         <v>152.22678458622877</v>
       </c>
       <c r="L321" s="12"/>
-      <c r="N321" s="21"/>
-    </row>
-    <row r="322" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N321" s="20"/>
+    </row>
+    <row r="322" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A322" s="9">
         <v>45170</v>
       </c>
@@ -11206,9 +10343,9 @@
         <v>155.56696146557178</v>
       </c>
       <c r="L322" s="12"/>
-      <c r="N322" s="21"/>
-    </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N322" s="20"/>
+    </row>
+    <row r="323" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A323" s="9">
         <v>45200</v>
       </c>
@@ -11219,7 +10356,7 @@
         <v>0.375</v>
       </c>
       <c r="D323" s="11" t="str">
-        <f t="shared" ref="D323:D354" si="5">IF(
+        <f t="shared" ref="D323:D355" si="5">IF(
  AND(
   B323 &gt;= IF(
          YEAR(B323)&gt;=2007,
@@ -11259,9 +10396,9 @@
         <v>150.33164876816181</v>
       </c>
       <c r="L323" s="12"/>
-      <c r="N323" s="21"/>
-    </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N323" s="20"/>
+    </row>
+    <row r="324" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A324" s="9">
         <v>45231</v>
       </c>
@@ -11297,9 +10434,9 @@
         <v>147.18888186986743</v>
       </c>
       <c r="L324" s="12"/>
-      <c r="N324" s="21"/>
-    </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N324" s="20"/>
+    </row>
+    <row r="325" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A325" s="9">
         <v>45261</v>
       </c>
@@ -11335,9 +10472,9 @@
         <v>147.05464308275435</v>
       </c>
       <c r="L325" s="12"/>
-      <c r="N325" s="21"/>
-    </row>
-    <row r="326" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N325" s="20"/>
+    </row>
+    <row r="326" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A326" s="9">
         <v>45292</v>
       </c>
@@ -11373,9 +10510,9 @@
         <v>146.38344914718897</v>
       </c>
       <c r="L326" s="12"/>
-      <c r="N326" s="21"/>
-    </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N326" s="20"/>
+    </row>
+    <row r="327" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A327" s="9">
         <v>45323</v>
       </c>
@@ -11411,9 +10548,9 @@
         <v>146.86512950094766</v>
       </c>
       <c r="L327" s="12"/>
-      <c r="N327" s="21"/>
-    </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N327" s="20"/>
+    </row>
+    <row r="328" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A328" s="9">
         <v>45352</v>
       </c>
@@ -11449,9 +10586,9 @@
         <v>146.82564750473793</v>
       </c>
       <c r="L328" s="12"/>
-      <c r="N328" s="21"/>
-    </row>
-    <row r="329" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N328" s="20"/>
+    </row>
+    <row r="329" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A329" s="9">
         <v>45383</v>
       </c>
@@ -11487,9 +10624,9 @@
         <v>142.45104232470001</v>
       </c>
       <c r="L329" s="12"/>
-      <c r="N329" s="21"/>
-    </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N329" s="20"/>
+    </row>
+    <row r="330" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A330" s="9">
         <v>45413</v>
       </c>
@@ -11525,9 +10662,9 @@
         <v>141.02179406190785</v>
       </c>
       <c r="L330" s="12"/>
-      <c r="N330" s="21"/>
-    </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N330" s="20"/>
+    </row>
+    <row r="331" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A331" s="9">
         <v>45444</v>
       </c>
@@ -11563,9 +10700,9 @@
         <v>140.61118130132667</v>
       </c>
       <c r="L331" s="12"/>
-      <c r="N331" s="21"/>
-    </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N331" s="20"/>
+    </row>
+    <row r="332" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A332" s="9">
         <v>45474</v>
       </c>
@@ -11601,9 +10738,9 @@
         <v>145.19109286165514</v>
       </c>
       <c r="L332" s="12"/>
-      <c r="N332" s="21"/>
-    </row>
-    <row r="333" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N332" s="20"/>
+    </row>
+    <row r="333" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A333" s="16">
         <v>45505</v>
       </c>
@@ -11639,9 +10776,9 @@
         <v>147.73373341756167</v>
       </c>
       <c r="L333" s="17"/>
-      <c r="N333" s="21"/>
-    </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N333" s="20"/>
+    </row>
+    <row r="334" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A334" s="16">
         <v>45536</v>
       </c>
@@ -11677,9 +10814,9 @@
         <v>146.72299431459263</v>
       </c>
       <c r="L334" s="17"/>
-      <c r="N334" s="21"/>
-    </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N334" s="20"/>
+    </row>
+    <row r="335" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A335" s="9">
         <v>45566</v>
       </c>
@@ -11715,9 +10852,9 @@
         <v>145.12792166771959</v>
       </c>
       <c r="L335" s="17"/>
-      <c r="N335" s="21"/>
-    </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N335" s="20"/>
+    </row>
+    <row r="336" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A336" s="9">
         <v>45597</v>
       </c>
@@ -11753,9 +10890,9 @@
         <v>146.99936828806071</v>
       </c>
       <c r="L336" s="17"/>
-      <c r="N336" s="21"/>
-    </row>
-    <row r="337" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N336" s="20"/>
+    </row>
+    <row r="337" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A337" s="9">
         <v>45627</v>
       </c>
@@ -11791,9 +10928,9 @@
         <v>146.26500315855975</v>
       </c>
       <c r="L337" s="17"/>
-      <c r="N337" s="21"/>
-    </row>
-    <row r="338" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N337" s="20"/>
+    </row>
+    <row r="338" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A338" s="16">
         <v>45658</v>
       </c>
@@ -11829,9 +10966,9 @@
         <v>146.88881869867345</v>
       </c>
       <c r="L338" s="17"/>
-      <c r="N338" s="21"/>
-    </row>
-    <row r="339" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N338" s="20"/>
+    </row>
+    <row r="339" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A339" s="16">
         <v>45689</v>
       </c>
@@ -11867,9 +11004,9 @@
         <v>146.09128237523694</v>
       </c>
       <c r="L339" s="17"/>
-      <c r="N339" s="21"/>
-    </row>
-    <row r="340" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N339" s="20"/>
+    </row>
+    <row r="340" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A340" s="16">
         <v>45717</v>
       </c>
@@ -11905,9 +11042,9 @@
         <v>145.50694883133298</v>
       </c>
       <c r="L340" s="17"/>
-      <c r="N340" s="21"/>
-    </row>
-    <row r="341" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N340" s="20"/>
+    </row>
+    <row r="341" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A341" s="16">
         <v>45748</v>
       </c>
@@ -11943,9 +11080,9 @@
         <v>149.16298168035382</v>
       </c>
       <c r="L341" s="17"/>
-      <c r="N341" s="21"/>
-    </row>
-    <row r="342" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N341" s="20"/>
+    </row>
+    <row r="342" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A342" s="16">
         <v>45778</v>
       </c>
@@ -11981,9 +11118,9 @@
         <v>146.42293114339867</v>
       </c>
       <c r="L342" s="17"/>
-      <c r="N342" s="21"/>
-    </row>
-    <row r="343" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N342" s="20"/>
+    </row>
+    <row r="343" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A343" s="16">
         <v>45809</v>
       </c>
@@ -12019,9 +11156,9 @@
         <v>148.49178774478844</v>
       </c>
       <c r="L343" s="17"/>
-      <c r="N343" s="21"/>
-    </row>
-    <row r="344" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N343" s="20"/>
+    </row>
+    <row r="344" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A344" s="16">
         <v>45839</v>
       </c>
@@ -12057,9 +11194,9 @@
         <v>148.67340492735318</v>
       </c>
       <c r="L344" s="17"/>
-      <c r="N344" s="21"/>
-    </row>
-    <row r="345" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N344" s="20"/>
+    </row>
+    <row r="345" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A345" s="16">
         <v>45870</v>
       </c>
@@ -12095,9 +11232,9 @@
         <v>149.7315224257739</v>
       </c>
       <c r="L345" s="17"/>
-      <c r="N345" s="21"/>
-    </row>
-    <row r="346" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N345" s="20"/>
+    </row>
+    <row r="346" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A346" s="16">
         <v>45901</v>
       </c>
@@ -12133,9 +11270,9 @@
         <v>148.26279216677202</v>
       </c>
       <c r="L346" s="17"/>
-      <c r="N346" s="21"/>
-    </row>
-    <row r="347" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N346" s="20"/>
+    </row>
+    <row r="347" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A347" s="16">
         <v>45931</v>
       </c>
@@ -12171,9 +11308,9 @@
         <v>144.95420088439678</v>
       </c>
       <c r="L347" s="17"/>
-      <c r="N347" s="21"/>
-    </row>
-    <row r="348" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N347" s="20"/>
+    </row>
+    <row r="348" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A348" s="16">
         <v>45962</v>
       </c>
@@ -12209,9 +11346,9 @@
         <v>146.80985470625401</v>
       </c>
       <c r="L348" s="17"/>
-      <c r="N348" s="21"/>
-    </row>
-    <row r="349" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N348" s="20"/>
+    </row>
+    <row r="349" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A349" s="16">
         <v>45992</v>
       </c>
@@ -12247,9 +11384,9 @@
         <v>146.88881869867348</v>
       </c>
       <c r="L349" s="17"/>
-      <c r="N349" s="21"/>
-    </row>
-    <row r="350" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N349" s="20"/>
+    </row>
+    <row r="350" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A350" s="16">
         <v>46023</v>
       </c>
@@ -12285,9 +11422,9 @@
         <v>150.15003158559702</v>
       </c>
       <c r="L350" s="17"/>
-      <c r="N350" s="21"/>
-    </row>
-    <row r="351" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N350" s="20"/>
+    </row>
+    <row r="351" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A351" s="16">
         <v>46054</v>
       </c>
@@ -12323,9 +11460,9 @@
         <v>151.5082122552117</v>
       </c>
       <c r="L351" s="17"/>
-      <c r="N351" s="21"/>
-    </row>
-    <row r="352" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N351" s="20"/>
+    </row>
+    <row r="352" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A352" s="9">
         <v>46082</v>
       </c>
@@ -12360,9 +11497,9 @@
       <c r="K352" s="1">
         <v>154.20878079595713</v>
       </c>
-      <c r="N352" s="21"/>
-    </row>
-    <row r="353" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N352" s="20"/>
+    </row>
+    <row r="353" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A353" s="9">
         <v>46113</v>
       </c>
@@ -12397,9 +11534,9 @@
       <c r="K353" s="1">
         <v>150.81332912192048</v>
       </c>
-      <c r="N353" s="21"/>
-    </row>
-    <row r="354" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N353" s="20"/>
+    </row>
+    <row r="354" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A354" s="9">
         <v>46143</v>
       </c>
@@ -12434,28 +11571,62 @@
       <c r="K354" s="1">
         <v>150.75805432722686</v>
       </c>
-      <c r="N354" s="21"/>
-    </row>
-    <row r="355" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="N355" s="21"/>
-    </row>
-    <row r="356" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="N356" s="21"/>
-    </row>
-    <row r="357" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="N357" s="21"/>
-    </row>
-    <row r="358" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="N358" s="21"/>
-    </row>
-    <row r="359" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="N359" s="21"/>
-    </row>
-    <row r="360" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="N360" s="21"/>
-    </row>
-    <row r="361" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="N361" s="21"/>
+      <c r="N354" s="20"/>
+    </row>
+    <row r="355" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A355" s="9">
+        <v>46174</v>
+      </c>
+      <c r="B355" s="9">
+        <v>46211</v>
+      </c>
+      <c r="C355" s="10">
+        <v>0.375</v>
+      </c>
+      <c r="D355" s="11" t="str">
+        <f t="shared" si="5"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E355" s="1">
+        <v>212.85667431944884</v>
+      </c>
+      <c r="F355" s="2">
+        <v>19470</v>
+      </c>
+      <c r="G355" s="2">
+        <v>19688</v>
+      </c>
+      <c r="H355" s="2">
+        <v>30432</v>
+      </c>
+      <c r="I355" s="2">
+        <v>19125</v>
+      </c>
+      <c r="J355" s="1">
+        <v>216.09032166441804</v>
+      </c>
+      <c r="K355" s="1">
+        <v>151.01863550221108</v>
+      </c>
+      <c r="N355" s="20"/>
+    </row>
+    <row r="356" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N356" s="20"/>
+    </row>
+    <row r="357" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N357" s="20"/>
+    </row>
+    <row r="358" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N358" s="20"/>
+    </row>
+    <row r="359" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N359" s="20"/>
+    </row>
+    <row r="360" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N360" s="20"/>
+    </row>
+    <row r="361" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N361" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12466,20 +11637,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D15FD8D4-D554-4318-A394-AC69A9CC97B1}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="19" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
@@ -12496,6 +11667,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Description xmlns="0bd4d3c9-04aa-442a-9f03-e370d3888c8a" xsi:nil="true"/>
+    <TaxCatchAll xmlns="6bdde3b2-7d08-4106-9f53-5b5c490aab7c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0bd4d3c9-04aa-442a-9f03-e370d3888c8a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BA02CEE7E06592488AB9FB206B163FCE" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d93301254c9a61fd9ec1c786889d2043">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0bd4d3c9-04aa-442a-9f03-e370d3888c8a" xmlns:ns3="6bdde3b2-7d08-4106-9f53-5b5c490aab7c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3b4d0496092f7727c4ca0d2dd8128c72" ns2:_="" ns3:_="">
     <xsd:import namespace="0bd4d3c9-04aa-442a-9f03-e370d3888c8a"/>
@@ -12758,18 +11941,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Description xmlns="0bd4d3c9-04aa-442a-9f03-e370d3888c8a" xsi:nil="true"/>
-    <TaxCatchAll xmlns="6bdde3b2-7d08-4106-9f53-5b5c490aab7c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0bd4d3c9-04aa-442a-9f03-e370d3888c8a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -12780,6 +11951,23 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6843BC72-CB58-4F86-B514-3B52D4772C3F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="6bdde3b2-7d08-4106-9f53-5b5c490aab7c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="0bd4d3c9-04aa-442a-9f03-e370d3888c8a"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A053C9B4-F58E-49F8-9C05-2F9558B34822}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12798,23 +11986,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6843BC72-CB58-4F86-B514-3B52D4772C3F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="6bdde3b2-7d08-4106-9f53-5b5c490aab7c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="0bd4d3c9-04aa-442a-9f03-e370d3888c8a"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE9CA77C-FCD5-4033-B7FF-8909DEC82D18}">
   <ds:schemaRefs>
